--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Barclays Bank UK Group — Cash Flow Summary by Year</a:t>
+              <a:t>Barclays Bank UK Group — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Barclays Bank UK Group — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Barclays Bank UK Group — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Barclays Bank UK Group — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£m)</t>
+          <t>Balance Sheet Summary (£m)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,294 +1821,294 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-7860</v>
+        <v>302824</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1959</v>
+        <v>303179</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-17451</v>
+        <v>293559</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1466</v>
+        <v>312179</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29314</v>
+        <v>319695</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29314</v>
+        <v>319695</v>
       </c>
       <c r="K6" t="n">
-        <v>1466</v>
+        <v>312179</v>
       </c>
       <c r="L6" t="n">
-        <v>-17451</v>
+        <v>293559</v>
       </c>
       <c r="M6" t="n">
-        <v>1959</v>
+        <v>303179</v>
       </c>
       <c r="N6" t="n">
-        <v>-7860</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>302824</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>15.2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>14.7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>14.8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>14.2</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>14.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from investing activities</t>
+          <t>Loans and advances at amortised cost to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>330</v>
+        <v>215634</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-7308</v>
+        <v>206435</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-2830</v>
+        <v>200782</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-12601</v>
+        <v>203279</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>6430</v>
+        <v>220271</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from investing activities</t>
+          <t>Loans and advances at amortised cost to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6430</v>
+        <v>220271</v>
       </c>
       <c r="K7" t="n">
-        <v>-12601</v>
+        <v>203279</v>
       </c>
       <c r="L7" t="n">
-        <v>-2830</v>
+        <v>200782</v>
       </c>
       <c r="M7" t="n">
-        <v>-7308</v>
+        <v>206435</v>
       </c>
       <c r="N7" t="n">
-        <v>330</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>215634</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>18.8</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>18.2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>18.1</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>17.1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>17.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
+          <t>Deposits at amortised cost from customers</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-1009</v>
+        <v>244666</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>660</v>
+        <v>244376</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1565</v>
+        <v>241218</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-3161</v>
+        <v>258058</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-785</v>
+        <v>260732</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
+          <t>Deposits at amortised cost from customers</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-785</v>
+        <v>260732</v>
       </c>
       <c r="K8" t="n">
-        <v>-3161</v>
+        <v>258058</v>
       </c>
       <c r="L8" t="n">
-        <v>1565</v>
+        <v>241218</v>
       </c>
       <c r="M8" t="n">
-        <v>660</v>
+        <v>244376</v>
       </c>
       <c r="N8" t="n">
-        <v>-1009</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>244666</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>21.8</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>21.6</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>20.5</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>27136</v>
+        <v>20278</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>35675</v>
+        <v>18585</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>40364</v>
+        <v>16861</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>59080</v>
+        <v>15413</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>73376</v>
+        <v>17400</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>73376</v>
+        <v>17400</v>
       </c>
       <c r="K9" t="n">
-        <v>59080</v>
+        <v>15413</v>
       </c>
       <c r="L9" t="n">
-        <v>40364</v>
+        <v>16861</v>
       </c>
       <c r="M9" t="n">
-        <v>35675</v>
+        <v>18585</v>
       </c>
       <c r="N9" t="n">
-        <v>27136</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>20278</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>5.3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>5.2</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>5.3</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>5.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>204</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>186</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>180</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>202</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>186.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£m)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>168</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>165</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>159.3</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>152.4</v>
       </c>
     </row>
@@ -1478,201 +2143,855 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>8811</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8423</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7670</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7397</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6482</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>6482</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7397</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7670</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8423</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8811</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-5093</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4511</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4567</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4577</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4691</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-4691</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-4577</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-4567</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-4511</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-5093</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2594</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2620</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1922</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1807</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1869</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>1869</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1807</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1922</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2620</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>18585</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>16861</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>15413</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>17027</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>17027</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>17400</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>15413</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>16861</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18585</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3050</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1030</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-106</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3050</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2875</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-1805</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-1602</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-1881</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-657</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-657</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1881</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-1602</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1805</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>20278</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>18585</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>16861</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>15413</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>17400</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>15413</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>16861</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>18585</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>20278</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-7860</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1959</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-17451</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1466</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>29314</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>29314</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1466</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-17451</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1959</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-7860</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-7308</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-2830</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-12601</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>6430</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>6430</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-12601</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-2830</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-7308</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-1009</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>660</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1565</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-3161</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-785</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>-785</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-3161</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1565</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>660</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-1009</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>27136</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>35675</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>40364</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>59080</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>73376</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>73376</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>59080</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>40364</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>35675</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>27136</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>14.5%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>14.8%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>14.7%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>17.1%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>17.1%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>18.1%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>18.2%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>18.8%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>20.5%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>21.6%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>21.8%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>23.1%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>5.3%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>5.3%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>5.6%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>186.6%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>202.0%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>180%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>186%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>204%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>152.4%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>159.3%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>165%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>168%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Leverage ratio shown on the 'excluding claims on central banks' basis for comparability across years (see Leverage Ratio sheet for the 'including' variant and FY2021 basis note).</t>
         </is>
@@ -1680,7 +2999,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1688,6 +3007,673 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>16996</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>17155</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15596</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>15828</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>16442</v>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>85065</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>83639</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>72102</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>72719</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>71213</v>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK PLC — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group (consolidated basis), £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding counterparty credit risk)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>68166</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>68018</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>58174</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>58885</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>54981</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>419</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>541</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1083</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Securitisation exposures (non-trading book, after cap)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2517</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1644</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1437</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Position, foreign exchange and commodities risks (Market risk)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>13905</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>13330</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>11668</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>11081</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>10892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Amounts below thresholds for deduction (subject to 250% risk weight)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2309</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2271</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2314</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2704</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>85065</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>83639</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>72102</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>72719</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>71213</v>
+      </c>
+    </row>
+    <row r="12" ht="200" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.16-17 (Table 10: OV1 - Overview of risk weighted exposure amounts) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.16-17 (Table 10: OV1 - Overview of risk weighted exposure amounts) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.12-13 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1862,7 +3848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2027,7 +4013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2188,7 +4174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2315,6 +4301,2564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK PLC — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group (consolidated basis), £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>21208</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>29819</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>34948</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>54208</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>69488</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Cash collateral and settlement balances</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6120</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6002</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5507</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5194</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities at amortised cost</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>13492</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>17983</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>17794</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>18537</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost to banks</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>281</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1213</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1391</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost to customers</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>215634</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>206435</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>200782</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>203279</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost (combined, as reported)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>220271</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Reverse repurchase agreements and other similar secured lending at amortised cost</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>6001</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5894</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3567</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>477</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Trading portfolio assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through the income statement</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1413</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1543</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1716</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>890</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1901</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1566</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>611</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>31572</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>27045</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>20409</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>19970</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>14945</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Goodwill and intangible assets</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3933</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>3948</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>3870</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>3528</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>287</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>261</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>382</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>884</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1212</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1916</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit assets</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>708</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>635</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>587</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>652</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>302824</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>303179</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>293559</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>312179</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>319695</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deposits at amortised cost from banks</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Deposits at amortised cost from customers</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>244666</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>244376</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>241218</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>258058</v>
+      </c>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Deposits at amortised cost (combined, as reported)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>260732</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Cash collateral and settlement balances</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>828</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>1779</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>553</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Repurchase agreements and other similar secured borrowing at amortised cost</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>13600</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>15506</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>15265</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>17702</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>18160</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities in issue</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>4703</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2619</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>3307</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>8009</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>8684</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>14049</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>13512</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>11499</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>9516</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Trading portfolio liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>908</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>726</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>908</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>464</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Financial liabilities designated at fair value</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>2848</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>398</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>962</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Current tax liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>598</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>954</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>540</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>578</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>338</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>1507</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>1566</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>1627</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>1775</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>282546</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>284594</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>276698</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>296766</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>302295</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital and share premium</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>2425</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2429</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>2560</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>-38</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>-896</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>-2279</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>-366</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>18084</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>17051</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>15578</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>15127</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>15201</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>20278</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>18585</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>16861</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>15413</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>302824</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>303179</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>293559</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>312179</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>319695</v>
+      </c>
+    </row>
+    <row r="45" ht="200" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, pp.197 (income statement), 199 (balance sheet), 200 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, pp.162 (income statement), 164 (balance sheet), 165 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
+FY2021: Barclays Bank UK PLC Annual Report 2021, pp.134 (income statement), 136 (balance sheet), 137 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
+Balance sheet note: FY2021 does not split loans and advances at amortised cost into a bank/customer split, does not disclose a separate debt securities at amortised cost line, and reports deposits at amortised cost as a single combined line - the combined figures appear on their own row for that year only; FY2022-2025 all split these. Income statement note: FY2021 places credit impairment releases/(charges) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; both years' own subtotals are reproduced as reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A45:F45"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK PLC — Consolidated Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group (consolidated basis), £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest and similar income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>13136</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>12588</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11024</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6981</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>5775</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest and similar expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-5371</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-5851</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-4597</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-1340</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-769</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7765</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>6737</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6427</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5641</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1565</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1507</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1605</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1689</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-482</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-411</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-370</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-322</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-219</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1083</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1235</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1367</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net trading income/(expense)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-48</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Net investment income/(expense)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>-91</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Gain on acquisition</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>558</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>8811</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8423</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7670</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7397</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6482</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Credit impairment releases/(charges) (pre-opex, FY2021 only)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income (FY2021 only)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n">
+        <v>6853</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-1555</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1209</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-1170</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1392</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure costs</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-300</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-258</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-343</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-385</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-389</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Administration and general expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-3104</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-2939</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-3024</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-2977</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-2859</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>UK regulatory levies</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-78</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Litigation and conduct / provisions for litigation and conduct</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-49</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-45</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-5093</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-4511</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-4567</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-4577</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-4691</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Loss on disposal of subsidiaries, associates and joint ventures</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>-124</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Profit on disposal of subsidiaries, associates and joint ventures (FY2021 only)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Profit before impairment (FY2022-FY2025 only)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3718</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>3912</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2979</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2820</v>
+      </c>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Credit impairment (charges)/releases (post-opex, FY2022-FY2025)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>-393</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>-352</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-308</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-268</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3325</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2552</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Taxation</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-731</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-940</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-749</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-745</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-294</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2594</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>2620</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1922</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1807</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="33" ht="200" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, pp.197 (income statement), 199 (balance sheet), 200 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, pp.162 (income statement), 164 (balance sheet), 165 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
+FY2021: Barclays Bank UK PLC Annual Report 2021, pp.134 (income statement), 136 (balance sheet), 137 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
+Balance sheet note: FY2021 does not split loans and advances at amortised cost into a bank/customer split, does not disclose a separate debt securities at amortised cost line, and reports deposits at amortised cost as a single combined line - the combined figures appear on their own row for that year only; FY2022-2025 all split these. Income statement note: FY2021 places credit impairment releases/(charges) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; both years' own subtotals are reproduced as reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A33:F33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK PLC — Consolidated Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group (consolidated basis), £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Called up share capital and share premium</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>473</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>13989</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>17027</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>1696</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>-67</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>-772</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n">
+        <v>-772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2021)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-839</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1696</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>-173</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>-173</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of employee share schemes</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>-510</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-510</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Capital contribution from Barclays PLC</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-366</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>15201</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>1634</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>-198</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>-1715</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2022)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-1913</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1634</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-106</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>-173</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n">
+        <v>-173</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-1715</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-2279</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>15127</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>15413</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n">
+        <v>1745</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1128</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n">
+        <v>-131</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-129</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n">
+        <v>-177</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>-177</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n">
+        <v>-1305</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-1305</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>2429</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>15578</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>16861</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n">
+        <v>2422</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>2422</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Issue and exchange of other equity</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n">
+        <v>-198</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n">
+        <v>-975</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>-975</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>2425</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>-896</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>17051</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>18585</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n">
+        <v>752</v>
+      </c>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Pension remeasurement</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>2426</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>-207</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n">
+        <v>-214</v>
+      </c>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n">
+        <v>-214</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n">
+        <v>-1425</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>-1425</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>2227</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>-38</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>18084</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>20278</v>
+      </c>
+    </row>
+    <row r="60" ht="200" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, pp.197 (income statement), 199 (balance sheet), 200 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, pp.162 (income statement), 164 (balance sheet), 165 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
+FY2021: Barclays Bank UK PLC Annual Report 2021, pp.134 (income statement), 136 (balance sheet), 137 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
+Balance sheet note: FY2021 does not split loans and advances at amortised cost into a bank/customer split, does not disclose a separate debt securities at amortised cost line, and reports deposits at amortised cost as a single combined line - the combined figures appear on their own row for that year only; FY2022-2025 all split these. Income statement note: FY2021 places credit impairment releases/(charges) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; both years' own subtotals are reproduced as reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A60:F60"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3463,16 +8007,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3483,413 +8027,373 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — CET1 Capital</t>
+          <t>Barclays Bank UK PLC — Asset Quality / Credit Risk Disclosures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Barclays Bank UK Group (consolidated basis), £m unless stated. Loans and advances at amortised cost, excluding debt securities at amortised cost.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£m)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£m)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£m)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£m)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£m)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>12331</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>11895</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>10638</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>10701</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>10828</v>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost, gross exposure by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>194856</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>179441</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>173805</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>175260</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>193961</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>19509</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>25400</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>26471</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>27637</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>24639</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (incl. POCI where separately disclosed)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3121</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3482</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3375</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3482</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total gross exposure</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>217486</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>208323</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>203651</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>206379</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>222450</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Impairment allowance by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>339</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>667</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>679</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>782</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>815</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (incl. POCI where separately disclosed)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>634</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>495</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>579</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>555</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total impairment allowance</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1607</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1656</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1709</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>NPL ratio (Stage 3 gross / total gross exposure)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage ratio (Stage 3 allowance / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Total coverage ratio (total allowance / total gross exposure)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="200" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group 'Loans and advances at amortised cost by product' tables ('Total loans and advances at amortised cost' row, excl. debt securities):
+FY2025: Annual Report 2025, p.103 — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
+FY2024: Annual Report 2025, p.104 (comparative) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
+FY2023: Annual Report 2023, p.82 — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
+FY2022: Annual Report 2023, p.83 (comparative) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
+FY2021: Annual Report 2021, p.66 — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
+Note: NPL/coverage ratios are computed here (not the report's own headline ratio, though they tie closely to it - e.g. FY2021 Stage 3 coverage of 21.1% matches the report's own 'Total' Stage 3 coverage figure exactly). Product-level breakdown (e.g. mortgages vs. cards vs. corporate) isn't reproduced since the product taxonomy changed between FY2021 (Home loans / Credit cards &amp; other retail / Wholesale loans) and FY2022-2025 (Retail mortgages / Retail credit cards / Retail other / Corporate loans) - see each year's own source page for the full by-product split.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>14.5%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>14.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>14.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, £m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>14558</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>14320</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>13067</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>13261</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13388</v>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3915,7 +8419,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total Capital</t>
+          <t>Barclays Bank UK Group — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3961,23 +8465,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>16996</v>
+        <v>12331</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>17155</v>
+        <v>11895</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>15596</v>
+        <v>10638</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>15828</v>
+        <v>10701</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>16442</v>
+        <v>10828</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -4018,7 +8522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total Capital Ratio</t>
+          <t>Barclays Bank UK Group — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -4064,32 +8568,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +8635,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total RWAs</t>
+          <t>Barclays Bank UK Group — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -4177,23 +8681,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>85065</v>
+        <v>14558</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>83639</v>
+        <v>14320</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>72102</v>
+        <v>13067</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>72719</v>
+        <v>13261</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>71213</v>
+        <v>13388</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">

--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -236,7 +236,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!L6</f>
             </strRef>
           </tx>
           <spPr>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$M$6:$T$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,7 +260,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!L7</f>
             </strRef>
           </tx>
           <spPr>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$M$7:$T$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,7 +284,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!L8</f>
             </strRef>
           </tx>
           <spPr>
@@ -294,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$M$8:$T$8</f>
             </numRef>
           </val>
         </ser>
@@ -308,7 +308,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!I9</f>
+              <f>'Overview'!L9</f>
             </strRef>
           </tx>
           <spPr>
@@ -318,12 +318,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$M$5:$T$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
+              <f>'Overview'!$M$9:$T$9</f>
             </numRef>
           </val>
         </ser>
@@ -434,7 +434,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!W13</f>
             </strRef>
           </tx>
           <spPr>
@@ -444,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$X$12:$AE$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$X$13:$AE$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,7 +458,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!W14</f>
             </strRef>
           </tx>
           <spPr>
@@ -468,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$X$12:$AE$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$X$14:$AE$14</f>
             </numRef>
           </val>
         </ser>
@@ -482,7 +482,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q15</f>
+              <f>'Overview'!W15</f>
             </strRef>
           </tx>
           <spPr>
@@ -492,12 +492,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$X$12:$AE$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$15:$V$15</f>
+              <f>'Overview'!$X$15:$AE$15</f>
             </numRef>
           </val>
         </ser>
@@ -608,7 +608,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AH19</f>
             </strRef>
           </tx>
           <spPr>
@@ -618,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AI$19:$AP$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,7 +632,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AH20</f>
             </strRef>
           </tx>
           <spPr>
@@ -642,12 +642,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AI$20:$AP$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,7 +656,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AH21</f>
             </strRef>
           </tx>
           <spPr>
@@ -666,12 +666,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AI$21:$AP$21</f>
             </numRef>
           </val>
         </ser>
@@ -680,7 +680,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y22</f>
+              <f>'Overview'!AH22</f>
             </strRef>
           </tx>
           <spPr>
@@ -690,12 +690,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AI$18:$AP$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$22:$AD$22</f>
+              <f>'Overview'!$AI$22:$AP$22</f>
             </numRef>
           </val>
         </ser>
@@ -806,7 +806,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!AS26</f>
             </strRef>
           </tx>
           <spPr>
@@ -816,12 +816,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$AT$26:$BA$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!AS27</f>
             </strRef>
           </tx>
           <spPr>
@@ -840,12 +840,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$AT$27:$BA$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,7 +854,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!AS28</f>
             </strRef>
           </tx>
           <spPr>
@@ -864,12 +864,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$AT$28:$BA$28</f>
             </numRef>
           </val>
         </ser>
@@ -878,7 +878,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG29</f>
+              <f>'Overview'!AS29</f>
             </strRef>
           </tx>
           <spPr>
@@ -888,12 +888,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AT$25:$BA$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$29:$AL$29</f>
+              <f>'Overview'!$AT$29:$BA$29</f>
             </numRef>
           </val>
         </ser>
@@ -1003,7 +1003,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!BD6</f>
             </strRef>
           </tx>
           <spPr>
@@ -1021,12 +1021,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$BE$6:$BL$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1036,7 +1036,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!BD7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$BE$7:$BL$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1069,7 +1069,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO8</f>
+              <f>'Overview'!BD8</f>
             </strRef>
           </tx>
           <spPr>
@@ -1087,12 +1087,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$8:$AT$8</f>
+              <f>'Overview'!$BE$8:$BL$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1102,7 +1102,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO9</f>
+              <f>'Overview'!BD9</f>
             </strRef>
           </tx>
           <spPr>
@@ -1120,12 +1120,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$9:$AT$9</f>
+              <f>'Overview'!$BE$9:$BL$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1135,7 +1135,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO10</f>
+              <f>'Overview'!BD10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1153,12 +1153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$10:$AT$10</f>
+              <f>'Overview'!$BE$10:$BL$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1168,7 +1168,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO11</f>
+              <f>'Overview'!BD11</f>
             </strRef>
           </tx>
           <spPr>
@@ -1186,12 +1186,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BE$5:$BL$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$11:$AT$11</f>
+              <f>'Overview'!$BE$11:$BL$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1666,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:BL40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1675,9 +1675,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
@@ -1713,6 +1713,24 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="53"/>
+    <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
+    <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
+    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
+    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
+    <col hidden="1" width="13" customWidth="1" min="59" max="59"/>
+    <col hidden="1" width="13" customWidth="1" min="60" max="60"/>
+    <col hidden="1" width="13" customWidth="1" min="61" max="61"/>
+    <col hidden="1" width="13" customWidth="1" min="62" max="62"/>
+    <col hidden="1" width="13" customWidth="1" min="63" max="63"/>
+    <col hidden="1" width="13" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1767,52 +1785,97 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1839,44 +1902,71 @@
       <c r="F6" s="5" t="n">
         <v>319695</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>287498</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>258398</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>251305</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
+        <v>251305</v>
+      </c>
+      <c r="N6" t="n">
+        <v>258398</v>
+      </c>
+      <c r="O6" t="n">
+        <v>287498</v>
+      </c>
+      <c r="P6" t="n">
         <v>319695</v>
       </c>
-      <c r="K6" t="n">
+      <c r="Q6" t="n">
         <v>312179</v>
       </c>
-      <c r="L6" t="n">
+      <c r="R6" t="n">
         <v>293559</v>
       </c>
-      <c r="M6" t="n">
+      <c r="S6" t="n">
         <v>303179</v>
       </c>
-      <c r="N6" t="n">
+      <c r="T6" t="n">
         <v>302824</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="BE6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="BH6" t="n">
         <v>15.2</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="BI6" t="n">
         <v>14.7</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BJ6" t="n">
         <v>14.8</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BK6" t="n">
         <v>14.2</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BL6" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -1901,44 +1991,71 @@
       <c r="F7" s="5" t="n">
         <v>220271</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>211649</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>197569</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>188565</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Loans and advances at amortised cost to customers</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
+        <v>188565</v>
+      </c>
+      <c r="N7" t="n">
+        <v>197569</v>
+      </c>
+      <c r="O7" t="n">
+        <v>211649</v>
+      </c>
+      <c r="P7" t="n">
         <v>220271</v>
       </c>
-      <c r="K7" t="n">
+      <c r="Q7" t="n">
         <v>203279</v>
       </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
         <v>200782</v>
       </c>
-      <c r="M7" t="n">
+      <c r="S7" t="n">
         <v>206435</v>
       </c>
-      <c r="N7" t="n">
+      <c r="T7" t="n">
         <v>215634</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="BE7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="BH7" t="n">
         <v>18.8</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="BI7" t="n">
         <v>18.2</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BJ7" t="n">
         <v>18.1</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BK7" t="n">
         <v>17.1</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BL7" t="n">
         <v>17.1</v>
       </c>
     </row>
@@ -1963,44 +2080,71 @@
       <c r="F8" s="5" t="n">
         <v>260732</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>240535</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>205696</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>197485</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Deposits at amortised cost from customers</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
+        <v>197485</v>
+      </c>
+      <c r="N8" t="n">
+        <v>205696</v>
+      </c>
+      <c r="O8" t="n">
+        <v>240535</v>
+      </c>
+      <c r="P8" t="n">
         <v>260732</v>
       </c>
-      <c r="K8" t="n">
+      <c r="Q8" t="n">
         <v>258058</v>
       </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
         <v>241218</v>
       </c>
-      <c r="M8" t="n">
+      <c r="S8" t="n">
         <v>244376</v>
       </c>
-      <c r="N8" t="n">
+      <c r="T8" t="n">
         <v>244666</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="BE8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="BH8" t="n">
         <v>23.1</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="BI8" t="n">
         <v>21.8</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BJ8" t="n">
         <v>21.6</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BK8" t="n">
         <v>20.5</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BL8" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2025,66 +2169,102 @@
       <c r="F9" s="5" t="n">
         <v>17400</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="5" t="n">
+        <v>17027</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>16513</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>16943</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
+        <v>16943</v>
+      </c>
+      <c r="N9" t="n">
+        <v>16513</v>
+      </c>
+      <c r="O9" t="n">
+        <v>17027</v>
+      </c>
+      <c r="P9" t="n">
         <v>17400</v>
       </c>
-      <c r="K9" t="n">
+      <c r="Q9" t="n">
         <v>15413</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
         <v>16861</v>
       </c>
-      <c r="M9" t="n">
+      <c r="S9" t="n">
         <v>18585</v>
       </c>
-      <c r="N9" t="n">
+      <c r="T9" t="n">
         <v>20278</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="BE9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="BH9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BJ9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BK9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BL9" t="n">
         <v>5.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="AO10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="BE10" t="n">
+        <v>164</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>144</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH10" t="n">
         <v>204</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="BI10" t="n">
         <v>186</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BJ10" t="n">
         <v>180</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BK10" t="n">
         <v>202</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BL10" t="n">
         <v>186.6</v>
       </c>
     </row>
@@ -2094,21 +2274,21 @@
           <t>Profit &amp; Loss Summary (£m)</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="AQ11" t="n">
+      <c r="BI11" t="n">
         <v>168</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BJ11" t="n">
         <v>165</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BK11" t="n">
         <v>159.3</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BL11" t="n">
         <v>152.4</v>
       </c>
     </row>
@@ -2143,27 +2323,57 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2190,24 +2400,42 @@
       <c r="F13" s="5" t="n">
         <v>6482</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n">
+        <v>6424</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7322</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5606</v>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="X13" t="n">
+        <v>5606</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7322</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6424</v>
+      </c>
+      <c r="AA13" t="n">
         <v>6482</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
         <v>7397</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AC13" t="n">
         <v>7670</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AD13" t="n">
         <v>8423</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AE13" t="n">
         <v>8811</v>
       </c>
     </row>
@@ -2232,24 +2460,42 @@
       <c r="F14" s="5" t="n">
         <v>-4691</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n">
+        <v>-4646</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-5944</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-3434</v>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="X14" t="n">
+        <v>-3434</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-5944</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-4646</v>
+      </c>
+      <c r="AA14" t="n">
         <v>-4691</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AB14" t="n">
         <v>-4577</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AC14" t="n">
         <v>-4567</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AD14" t="n">
         <v>-4511</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AE14" t="n">
         <v>-5093</v>
       </c>
     </row>
@@ -2274,24 +2520,42 @@
       <c r="F15" s="5" t="n">
         <v>1869</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="G15" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Profit after tax</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="X15" t="n">
+        <v>1115</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>156</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>379</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1869</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AB15" t="n">
         <v>1807</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AC15" t="n">
         <v>1922</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AD15" t="n">
         <v>2620</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AE15" t="n">
         <v>2594</v>
       </c>
     </row>
@@ -2333,27 +2597,57 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2380,24 +2674,42 @@
       <c r="F19" s="5" t="n">
         <v>17027</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n">
+        <v>16513</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>16943</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AI19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>16943</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>16513</v>
+      </c>
+      <c r="AL19" t="n">
         <v>17027</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AM19" t="n">
         <v>17400</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AN19" t="n">
         <v>15413</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AO19" t="n">
         <v>16861</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AP19" t="n">
         <v>18585</v>
       </c>
     </row>
@@ -2422,24 +2734,42 @@
       <c r="F20" s="5" t="n">
         <v>1030</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>670</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1118</v>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>Total comprehensive income for the year</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AI20" t="n">
+        <v>1118</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>263</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>670</v>
+      </c>
+      <c r="AL20" t="n">
         <v>1030</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AM20" t="n">
         <v>-106</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AN20" t="n">
         <v>3050</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AO20" t="n">
         <v>2875</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AP20" t="n">
         <v>3498</v>
       </c>
     </row>
@@ -2464,24 +2794,42 @@
       <c r="F21" s="5" t="n">
         <v>-657</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n">
+        <v>-156</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-693</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>15779</v>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>Other movements, net</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AI21" t="n">
+        <v>15779</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-693</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AL21" t="n">
         <v>-657</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AM21" t="n">
         <v>-1881</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AN21" t="n">
         <v>-1602</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AO21" t="n">
         <v>-1151</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AP21" t="n">
         <v>-1805</v>
       </c>
     </row>
@@ -2506,24 +2854,42 @@
       <c r="F22" s="5" t="n">
         <v>17400</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="G22" s="5" t="n">
+        <v>17027</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>16513</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>16943</v>
+      </c>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AI22" t="n">
+        <v>16943</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16513</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>17027</v>
+      </c>
+      <c r="AL22" t="n">
         <v>17400</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AM22" t="n">
         <v>15413</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AN22" t="n">
         <v>16861</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AO22" t="n">
         <v>18585</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AP22" t="n">
         <v>20278</v>
       </c>
     </row>
@@ -2565,27 +2931,57 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2612,24 +3008,42 @@
       <c r="F26" s="5" t="n">
         <v>29314</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n">
+        <v>13976</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-3111</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-257</v>
+      </c>
+      <c r="AS26" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AT26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-3111</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13976</v>
+      </c>
+      <c r="AW26" t="n">
         <v>29314</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AX26" t="n">
         <v>1466</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AY26" t="n">
         <v>-17451</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AZ26" t="n">
         <v>1959</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="BA26" t="n">
         <v>-7860</v>
       </c>
     </row>
@@ -2654,24 +3068,42 @@
       <c r="F27" s="5" t="n">
         <v>6430</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n">
+        <v>-5574</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>-11876</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>45003</v>
+      </c>
+      <c r="AS27" t="inlineStr">
         <is>
           <t>Net cash from investing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AT27" t="n">
+        <v>45003</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-11876</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-5574</v>
+      </c>
+      <c r="AW27" t="n">
         <v>6430</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AX27" t="n">
         <v>-12601</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AY27" t="n">
         <v>-2830</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AZ27" t="n">
         <v>-7308</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="BA27" t="n">
         <v>330</v>
       </c>
     </row>
@@ -2696,24 +3128,42 @@
       <c r="F28" s="5" t="n">
         <v>-785</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n">
+        <v>2077</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-568</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>-465</v>
+      </c>
+      <c r="AS28" t="inlineStr">
         <is>
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AT28" t="n">
+        <v>-465</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>-568</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2077</v>
+      </c>
+      <c r="AW28" t="n">
         <v>-785</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AX28" t="n">
         <v>-3161</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AY28" t="n">
         <v>1565</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AZ28" t="n">
         <v>660</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="BA28" t="n">
         <v>-1009</v>
       </c>
     </row>
@@ -2738,24 +3188,42 @@
       <c r="F29" s="5" t="n">
         <v>73376</v>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="G29" s="5" t="n">
+        <v>38417</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>28042</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>44334</v>
+      </c>
+      <c r="AS29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AT29" t="n">
+        <v>44334</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>28042</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>38417</v>
+      </c>
+      <c r="AW29" t="n">
         <v>73376</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AX29" t="n">
         <v>59080</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AY29" t="n">
         <v>40364</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AZ29" t="n">
         <v>35675</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="BA29" t="n">
         <v>27136</v>
       </c>
     </row>
@@ -2797,6 +3265,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2829,6 +3312,21 @@
           <t>15.2%</t>
         </is>
       </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2861,6 +3359,21 @@
           <t>18.8%</t>
         </is>
       </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>17.0%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2893,6 +3406,21 @@
           <t>23.1%</t>
         </is>
       </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2925,6 +3453,21 @@
           <t>5.6%</t>
         </is>
       </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>4.9%*</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2957,6 +3500,21 @@
           <t>204%</t>
         </is>
       </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>160%</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>144%</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>164%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2989,17 +3547,32 @@
           <t>Not disclosed</t>
         </is>
       </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Leverage ratio shown on the 'excluding claims on central banks' basis for comparability across years (see Leverage Ratio sheet for the 'including' variant and FY2021 basis note).</t>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Leverage ratio shown on the 'excluding claims on central banks' basis for comparability across years (see Leverage Ratio sheet for the 'including' variant and FY2021-FY2018 basis notes); FY2018's figure (marked *) is instead the single 'CRR leverage ratio' disclosed that year (an 'including claims on central banks' basis), since no UK-basis 'excluding' equivalent was published for FY2018 - see the Leverage Ratio sheet's own note. FY2018's 'Other movements, net' in the equity roll-forward is dominated by the £13,044m ordinary share issue and capital reorganisation and £2,169m net equity impact of the UK banking business transfer that established Barclays Bank UK Group in April 2018, not a comparable year-on-year 'other movements' figure.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3012,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3021,6 +3594,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3068,6 +3644,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3098,6 +3689,21 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>18.8%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -3107,13 +3713,16 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3125,7 +3734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3134,6 +3743,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3181,6 +3793,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3202,6 +3829,15 @@
       </c>
       <c r="F4" s="6" t="n">
         <v>16442</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>17178</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>16012</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>16100</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -3210,13 +3846,16 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3228,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3237,6 +3876,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3284,6 +3926,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3314,6 +3971,21 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -3323,13 +3995,16 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3341,7 +4016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3350,6 +4025,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3397,6 +4075,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3418,6 +4111,15 @@
       </c>
       <c r="F4" s="6" t="n">
         <v>71213</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>72025</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>75010</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>75327</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -3426,13 +4128,16 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3444,7 +4149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -3453,6 +4158,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3500,6 +4208,21 @@
           <t>FY2021 (£m)</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3522,6 +4245,13 @@
       <c r="F4" s="6" t="n">
         <v>54981</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>56891</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>60490</v>
+      </c>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3544,6 +4274,13 @@
       <c r="F5" s="6" t="n">
         <v>1208</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>787</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3566,6 +4303,13 @@
       <c r="F6" s="6" t="n">
         <v>1268</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>737</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3588,6 +4332,13 @@
       <c r="F7" s="6" t="n">
         <v>100</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3610,6 +4361,13 @@
       <c r="F8" s="6" t="n">
         <v>10892</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>11347</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>11617</v>
+      </c>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3632,6 +4390,13 @@
       <c r="F9" s="6" t="n">
         <v>2764</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>2191</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1965</v>
+      </c>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3654,6 +4419,13 @@
       <c r="F10" s="5" t="n">
         <v>71213</v>
       </c>
+      <c r="G10" s="5" t="n">
+        <v>72025</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>75010</v>
+      </c>
+      <c r="I10" s="5" t="n"/>
     </row>
     <row r="12" ht="200" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -3661,13 +4433,17 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.16-17 (Table 10: OV1 - Overview of risk weighted exposure amounts) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.16-17 (Table 10: OV1 - Overview of risk weighted exposure amounts) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.12-13 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.12-13 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.11 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.11 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
+FY2018: not available - Barclays Bank UK PLC did not publish a standalone Pillar 3 report for FY2018 (see note above), and the FY2018 Annual Report's capital risk section discloses only the total RWA figure (£75,327m), not a by-risk-type breakdown.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3679,7 +4455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3688,6 +4464,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3735,6 +4514,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3757,6 +4551,13 @@
       <c r="F4" s="6" t="n">
         <v>241173</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>245176</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>236026</v>
+      </c>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3789,6 +4590,17 @@
           <t>5.6%</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3821,11 +4633,26 @@
           <t>4.1%</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from the 2021 Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports.</t>
+          <t>Note: FY2021-FY2019 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from each year's Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports. FY2018 predates that UK/CRR leverage ratio split at the BBUKPLC entity level (no standalone Pillar 3 report was published for FY2018 - see p3_sources note); the FY2018 Annual Report discloses only a single 'CRR leverage ratio' of 4.9% (with £258bn of CRR leverage exposure), which is presented here on the 'including claims on central banks' row as the closer equivalent - the 'excluding' row and exposure figure are left blank for FY2018 since no comparable UK-basis figure was disclosed that year.</t>
         </is>
       </c>
     </row>
@@ -3835,14 +4662,17 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures, 'Capital Requirements Regulation (CRR) leverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3854,7 +4684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3863,6 +4693,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3910,6 +4743,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3932,6 +4780,13 @@
       <c r="F4" s="6" t="n">
         <v>85092</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>58035</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>41293</v>
+      </c>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3954,6 +4809,13 @@
       <c r="F5" s="6" t="n">
         <v>41690</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>36246</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>28741</v>
+      </c>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3986,11 +4848,26 @@
           <t>204%</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>160%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>144%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>164%</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: LCR is computed as a trailing average of the last 12 month-end observations.</t>
+          <t>Note: LCR is computed as a trailing average of the last 12 month-end observations from FY2019 onward. FY2018 predates the BBUKPLC entity's first standalone Pillar 3 report; the FY2018 Annual Report discloses only the headline LCR ratio (164%) within its liquidity risk section, without the underlying weighted HQLA/net cash outflow components in the KM1 format used from FY2019 - those two rows are left blank for FY2018 for that reason.</t>
         </is>
       </c>
     </row>
@@ -4000,14 +4877,17 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.74 (Annual Report 2018 liquidity risk disclosures, 'Barclays Bank UK Group liquidity coverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4019,7 +4899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4028,6 +4908,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4075,6 +4958,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4095,6 +4993,9 @@
         <v>266421</v>
       </c>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4115,6 +5016,9 @@
         <v>158156</v>
       </c>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4147,11 +5051,26 @@
           <t>Not disclosed</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2021 figures are available.</t>
+          <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2018-FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2018-FY2021 figures are available.</t>
         </is>
       </c>
     </row>
@@ -4161,14 +5080,17 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4180,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4189,6 +5111,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4236,6 +5161,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4268,11 +5208,26 @@
           <t>Not disclosed at this level</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: MREL disclosures are not applicable for Barclays Bank UK Group (the ring-fenced entity) in any of the five years reviewed; MREL is disclosed at the Barclays PLC group level instead (see Barclays PLC Pillar 3 Report, Table 21: TLAC2).</t>
+          <t>Note: MREL disclosures are not applicable for Barclays Bank UK Group (the ring-fenced entity) in any of the eight years reviewed; MREL is disclosed at the Barclays PLC group level instead (see Barclays PLC Pillar 3 Report, Table 21: TLAC2).</t>
         </is>
       </c>
     </row>
@@ -4282,14 +5237,17 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4301,7 +5259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -4310,6 +5268,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4355,6 +5316,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
         </is>
       </c>
     </row>
@@ -4369,6 +5345,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4391,6 +5370,15 @@
       <c r="F5" s="6" t="n">
         <v>69488</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>35218</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>24305</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>40669</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4413,6 +5401,15 @@
       <c r="F6" s="6" t="n">
         <v>5067</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>4345</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4331</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3349</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4433,6 +5430,9 @@
         <v>18537</v>
       </c>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4453,6 +5453,9 @@
         <v>1391</v>
       </c>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4473,6 +5476,9 @@
         <v>203279</v>
       </c>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4487,6 +5493,15 @@
       <c r="F10" s="6" t="n">
         <v>220271</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>211649</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>197569</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>188565</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4509,6 +5524,15 @@
       <c r="F11" s="6" t="n">
         <v>65</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1761</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1759</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4531,6 +5555,15 @@
       <c r="F12" s="6" t="n">
         <v>169</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>298</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>860</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4553,6 +5586,15 @@
       <c r="F13" s="6" t="n">
         <v>2767</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>3432</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>3571</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>3880</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4575,6 +5617,15 @@
       <c r="F14" s="6" t="n">
         <v>890</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>241</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4597,6 +5648,15 @@
       <c r="F15" s="6" t="n">
         <v>14945</v>
       </c>
+      <c r="G15" s="6" t="n">
+        <v>26026</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>19322</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>6710</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4619,6 +5679,15 @@
       <c r="F16" s="6" t="n">
         <v>3526</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>3527</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>3530</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3534</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4641,549 +5710,776 @@
       <c r="F17" s="6" t="n">
         <v>562</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>737</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>893</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>498</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>884</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>1212</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1296</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>1916</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>1368</v>
-      </c>
+          <t>Current tax assets</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Retirement benefit assets</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
+        <v>884</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1212</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1916</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1368</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>780</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>810</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>792</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>Retirement benefit assets</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>Other assets</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B21" s="6" t="n">
         <v>708</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C21" s="6" t="n">
         <v>635</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D21" s="6" t="n">
         <v>587</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>652</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>577</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>302824</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>303179</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>293559</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>312179</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>319695</v>
+      <c r="G21" s="6" t="n">
+        <v>728</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1254</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1157</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>302824</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>303179</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>293559</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>312179</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>319695</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>287498</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>258398</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>251305</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Deposits at amortised cost from banks</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>125</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>59</v>
-      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Deposits at amortised cost from customers</t>
+          <t>Deposits at amortised cost from banks</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>244666</v>
+        <v>125</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>244376</v>
+        <v>85</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>241218</v>
+        <v>6</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>258058</v>
+        <v>59</v>
       </c>
       <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Deposits at amortised cost (combined, as reported)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n">
-        <v>260732</v>
-      </c>
+          <t>Deposits at amortised cost from customers</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>244666</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>244376</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>241218</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>258058</v>
+      </c>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Cash collateral and settlement balances</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>828</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>1779</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1370</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>553</v>
-      </c>
+          <t>Deposits at amortised cost (combined, as reported)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n">
-        <v>774</v>
+        <v>260732</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>240535</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>205696</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>197485</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Repurchase agreements and other similar secured borrowing at amortised cost</t>
+          <t>Cash collateral and settlement balances</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>13600</v>
+        <v>828</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>15506</v>
+        <v>1779</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>15265</v>
+        <v>1370</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>17702</v>
+        <v>553</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>18160</v>
+        <v>774</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>455</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Debt securities in issue</t>
+          <t>Repurchase agreements and other similar secured borrowing at amortised cost</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4703</v>
+        <v>13600</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>2619</v>
+        <v>15506</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3307</v>
+        <v>15265</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>8009</v>
+        <v>17702</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>8684</v>
+        <v>18160</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>7178</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>13420</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>11978</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Subordinated liabilities</t>
+          <t>Debt securities in issue</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>14049</v>
+        <v>4703</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>13512</v>
+        <v>2619</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>11499</v>
+        <v>3307</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>8268</v>
+        <v>8009</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>9516</v>
+        <v>8684</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>7503</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>8271</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>11172</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Trading portfolio liabilities</t>
+          <t>Subordinated liabilities</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>908</v>
+        <v>14049</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>726</v>
+        <v>13512</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>908</v>
+        <v>11499</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>464</v>
+        <v>8268</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>878</v>
+        <v>9516</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>9869</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>7688</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>7548</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Financial liabilities designated at fair value</t>
+          <t>Trading portfolio liabilities</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>1003</v>
+        <v>908</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2848</v>
+        <v>726</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>196</v>
-      </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
+        <v>908</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>464</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>878</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1704</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1269</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Financial liabilities designated at fair value</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>195</v>
+        <v>1003</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>300</v>
+        <v>2848</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>398</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>962</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>814</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Current tax liabilities</t>
+          <t>Derivative financial instruments</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>598</v>
+        <v>195</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>954</v>
+        <v>300</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>540</v>
+        <v>398</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>578</v>
+        <v>962</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>377</v>
+        <v>814</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Current tax liabilities</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>364</v>
+        <v>598</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>323</v>
+        <v>954</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>364</v>
+        <v>540</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>338</v>
+        <v>578</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>536</v>
+        <v>377</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>458</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>984</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>338</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>536</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
           <t>Other liabilities</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B36" s="6" t="n">
         <v>1507</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C36" s="6" t="n">
         <v>1566</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D36" s="6" t="n">
         <v>1627</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E36" s="6" t="n">
         <v>1775</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>1824</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>282546</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>284594</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>276698</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>296766</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>302295</v>
+      <c r="G36" s="6" t="n">
+        <v>1906</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>2034</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1888</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>282546</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>284594</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>276698</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>296766</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>302295</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>270471</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>241885</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>234362</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Called up share capital and share premium</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Other equity instruments</t>
+          <t>Called up share capital and share premium</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>2227</v>
+        <v>5</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>2425</v>
+        <v>5</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2429</v>
+        <v>5</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>2560</v>
+        <v>5</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2560</v>
+        <v>5</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Other equity instruments</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>-38</v>
+        <v>2227</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>-896</v>
+        <v>2425</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>-1151</v>
+        <v>2429</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-2279</v>
+        <v>2560</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-366</v>
+        <v>2560</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>2560</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>-38</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>-896</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>-2279</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>-366</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>473</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
           <t>Retained earnings</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B42" s="6" t="n">
         <v>18084</v>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C42" s="6" t="n">
         <v>17051</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D42" s="6" t="n">
         <v>15578</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E42" s="6" t="n">
         <v>15127</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>15201</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>20278</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>18585</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>16861</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>15413</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>17400</v>
+      <c r="G42" s="6" t="n">
+        <v>13989</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>13765</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>14792</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>20278</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>18585</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>16861</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>15413</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>17027</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>16513</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>16943</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B44" s="5" t="n">
         <v>302824</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="5" t="n">
         <v>303179</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D44" s="5" t="n">
         <v>293559</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E44" s="5" t="n">
         <v>312179</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F44" s="5" t="n">
         <v>319695</v>
       </c>
-    </row>
-    <row r="45" ht="200" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="G44" s="5" t="n">
+        <v>287498</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>258398</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>251305</v>
+      </c>
+    </row>
+    <row r="46" ht="200" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, pp.197 (income statement), 199 (balance sheet), 200 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, pp.162 (income statement), 164 (balance sheet), 165 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
 FY2021: Barclays Bank UK PLC Annual Report 2021, pp.134 (income statement), 136 (balance sheet), 137 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
-Balance sheet note: FY2021 does not split loans and advances at amortised cost into a bank/customer split, does not disclose a separate debt securities at amortised cost line, and reports deposits at amortised cost as a single combined line - the combined figures appear on their own row for that year only; FY2022-2025 all split these. Income statement note: FY2021 places credit impairment releases/(charges) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; both years' own subtotals are reproduced as reported.</t>
+FY2020: Barclays Bank UK PLC Annual Report 2020, pp.123 (income statement), 125 (balance sheet), 126 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays-Bank-UK-PLC-2020-Annual-Report.pdf
+FY2019: Barclays Bank UK PLC Annual Report 2019, pp.104 (income statement), 106 (balance sheet), 107 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Annual%20Report%202019.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, pp.105 (income statement), 107 (balance sheet), 108 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
+Balance sheet note: FY2018-FY2021 do not split loans and advances at amortised cost into a bank/customer split, do not disclose a separate debt securities at amortised cost line, and report deposits at amortised cost as a single combined line - the combined figures appear on their own row for those years only; FY2022-2025 all split these. FY2020 is the only year with a separate 'Current tax assets' line (a small net asset position; other years report a nil/immaterial current tax asset position folded into other lines). Income statement note: FY2018-FY2021 place credit impairment charges/(releases) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; each year's own subtotals are reproduced as reported. FY2020 and FY2021 both separately disclose a 'Profit on disposal of subsidiaries, associates and joint ventures' line before profit before tax. Figures for FY2018-FY2020 are each reproduced exactly as originally reported in that year's own Annual Report, not as later restated comparatives (e.g. Barclays restated FY2018's tax charge by £28m from FY2019 onward following an IAS 12 update on AT1 coupon tax relief) - consistent with this workbook's sourcing convention throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:I46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5195,7 +6491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -5204,6 +6500,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5249,6 +6548,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
         </is>
       </c>
     </row>
@@ -5263,6 +6577,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5285,6 +6602,15 @@
       <c r="F5" s="6" t="n">
         <v>5775</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>6201</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>7218</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>5267</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5307,6 +6633,15 @@
       <c r="F6" s="6" t="n">
         <v>-769</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>-1021</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-1413</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-830</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5329,6 +6664,15 @@
       <c r="F7" s="5" t="n">
         <v>5006</v>
       </c>
+      <c r="G7" s="5" t="n">
+        <v>5180</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5805</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4437</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5351,6 +6695,15 @@
       <c r="F8" s="6" t="n">
         <v>1466</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1674</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1315</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5373,6 +6726,15 @@
       <c r="F9" s="6" t="n">
         <v>-219</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>-310</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-368</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-273</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -5395,6 +6757,15 @@
       <c r="F10" s="5" t="n">
         <v>1247</v>
       </c>
+      <c r="G10" s="5" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1306</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5417,6 +6788,15 @@
       <c r="F11" s="6" t="n">
         <v>40</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5438,6 +6818,15 @@
       </c>
       <c r="F12" s="6" t="n">
         <v>181</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -5455,6 +6844,9 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5477,6 +6869,15 @@
       <c r="F14" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -5499,11 +6900,20 @@
       <c r="F15" s="5" t="n">
         <v>6482</v>
       </c>
+      <c r="G15" s="5" t="n">
+        <v>6424</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7322</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>5606</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Credit impairment releases/(charges) (pre-opex, FY2021 only)</t>
+          <t>Credit impairment releases/(charges) (pre-opex, FY2018-FY2021)</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -5513,11 +6923,20 @@
       <c r="F16" s="6" t="n">
         <v>371</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>-1427</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-709</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-624</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Net operating income (FY2021 only)</t>
+          <t>Net operating income (FY2018-FY2021)</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -5527,6 +6946,15 @@
       <c r="F17" s="5" t="n">
         <v>6853</v>
       </c>
+      <c r="G17" s="5" t="n">
+        <v>4997</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>6613</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>4982</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -5539,6 +6967,9 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5561,6 +6992,15 @@
       <c r="F19" s="6" t="n">
         <v>-1392</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>-1311</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1252</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-1016</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5583,6 +7023,15 @@
       <c r="F20" s="6" t="n">
         <v>-389</v>
       </c>
+      <c r="G20" s="6" t="n">
+        <v>-444</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-382</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-307</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5604,6 +7053,15 @@
       </c>
       <c r="F21" s="6" t="n">
         <v>-2859</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-2848</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-2724</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>-2033</v>
       </c>
     </row>
     <row r="22">
@@ -5621,6 +7079,9 @@
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5643,6 +7104,15 @@
       <c r="F23" s="6" t="n">
         <v>-51</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-1586</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -5664,6 +7134,15 @@
       </c>
       <c r="F24" s="5" t="n">
         <v>-4691</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-4646</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-5944</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-3434</v>
       </c>
     </row>
     <row r="25">
@@ -5681,11 +7160,14 @@
         <v>0</v>
       </c>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Profit on disposal of subsidiaries, associates and joint ventures (FY2021 only)</t>
+          <t>Profit on disposal of subsidiaries, associates and joint ventures (FY2020-FY2021 only)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
@@ -5695,6 +7177,11 @@
       <c r="F26" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="G26" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5715,6 +7202,9 @@
         <v>2820</v>
       </c>
       <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5735,6 +7225,9 @@
         <v>-268</v>
       </c>
       <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -5757,6 +7250,15 @@
       <c r="F29" s="5" t="n">
         <v>2163</v>
       </c>
+      <c r="G29" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1548</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5779,6 +7281,15 @@
       <c r="F30" s="6" t="n">
         <v>-294</v>
       </c>
+      <c r="G30" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>-513</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>-433</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -5800,6 +7311,15 @@
       </c>
       <c r="F31" s="5" t="n">
         <v>1869</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>1115</v>
       </c>
     </row>
     <row r="33" ht="200" customHeight="1">
@@ -5809,13 +7329,16 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, pp.197 (income statement), 199 (balance sheet), 200 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, pp.162 (income statement), 164 (balance sheet), 165 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
 FY2021: Barclays Bank UK PLC Annual Report 2021, pp.134 (income statement), 136 (balance sheet), 137 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
-Balance sheet note: FY2021 does not split loans and advances at amortised cost into a bank/customer split, does not disclose a separate debt securities at amortised cost line, and reports deposits at amortised cost as a single combined line - the combined figures appear on their own row for that year only; FY2022-2025 all split these. Income statement note: FY2021 places credit impairment releases/(charges) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; both years' own subtotals are reproduced as reported.</t>
+FY2020: Barclays Bank UK PLC Annual Report 2020, pp.123 (income statement), 125 (balance sheet), 126 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays-Bank-UK-PLC-2020-Annual-Report.pdf
+FY2019: Barclays Bank UK PLC Annual Report 2019, pp.104 (income statement), 106 (balance sheet), 107 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Annual%20Report%202019.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, pp.105 (income statement), 107 (balance sheet), 108 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
+Balance sheet note: FY2018-FY2021 do not split loans and advances at amortised cost into a bank/customer split, do not disclose a separate debt securities at amortised cost line, and report deposits at amortised cost as a single combined line - the combined figures appear on their own row for those years only; FY2022-2025 all split these. FY2020 is the only year with a separate 'Current tax assets' line (a small net asset position; other years report a nil/immaterial current tax asset position folded into other lines). Income statement note: FY2018-FY2021 place credit impairment charges/(releases) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; each year's own subtotals are reproduced as reported. FY2020 and FY2021 both separately disclose a 'Profit on disposal of subsidiaries, associates and joint ventures' line before profit before tax. Figures for FY2018-FY2020 are each reproduced exactly as originally reported in that year's own Annual Report, not as later restated comparatives (e.g. Barclays restated FY2018's tax charge by £28m from FY2019 onward following an IAS 12 update on AT1 coupon tax relief) - consistent with this workbook's sourcing convention throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A33:I33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5827,7 +7350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -5887,23 +7410,23 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Balance as at 1 January 2021</t>
+          <t>Balance as at 1 January 2018</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2560</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>473</v>
+        <v>20</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13989</v>
+        <v>21</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>17027</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -5914,14 +7437,14 @@
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n">
-        <v>1696</v>
+        <v>1010</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1869</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6">
@@ -5933,11 +7456,11 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n">
-        <v>-67</v>
+        <v>-17</v>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n">
-        <v>-67</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="7">
@@ -5949,905 +7472,1528 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n">
-        <v>-772</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n">
-        <v>-772</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year (FY2021)</t>
+          <t>Total comprehensive income for the year (FY2018)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-839</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1696</v>
+        <v>1010</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1030</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Employee share schemes</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
+          <t>Issue of new ordinary shares</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>13044</v>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n">
-        <v>37</v>
-      </c>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n">
-        <v>37</v>
+        <v>13044</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Other equity instruments coupons paid</t>
+          <t>Equity settled share schemes</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n">
-        <v>-173</v>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="E10" s="6" t="n">
+        <v>19</v>
+      </c>
       <c r="F10" s="6" t="n">
-        <v>-173</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Vesting of employee share schemes</t>
+          <t>Net equity impact of the UK banking business transfer</t>
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>2070</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>53</v>
+      </c>
       <c r="E11" s="6" t="n">
-        <v>-11</v>
+        <v>46</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-11</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
+          <t>Capital reorganisation</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-13044</v>
+      </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n">
-        <v>-510</v>
+        <v>13044</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>-510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Capital contribution from Barclays PLC</t>
+          <t>Other equity instruments coupons paid</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>-105</v>
+      </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>-77</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2021</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>2560</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>-366</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>15201</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>17400</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of employee share schemes</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax</t>
+          <t>Dividends paid</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n">
-        <v>173</v>
-      </c>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n">
-        <v>1634</v>
+        <v>-350</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1807</v>
+        <v>-350</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI reserve movement</t>
+          <t>Capital contribution from Barclays Bank PLC</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n">
-        <v>-198</v>
-      </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>983</v>
+      </c>
       <c r="F16" s="6" t="n">
-        <v>-198</v>
+        <v>983</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Cash flow hedges</t>
+          <t>Other reserve movements</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n">
-        <v>-1715</v>
-      </c>
-      <c r="E17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="F17" s="6" t="n">
-        <v>-1715</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year (FY2022)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
+          <t>Balance as at 31 December 2018</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="C18" s="5" t="n">
-        <v>173</v>
+        <v>2070</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-1913</v>
+        <v>76</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1634</v>
+        <v>14792</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-106</v>
+        <v>16943</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Employee share schemes</t>
+          <t>Profit after tax</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="6" t="n">
+        <v>153</v>
+      </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>22</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Other equity instruments coupons paid</t>
+          <t>Financial assets at FVOCI reserve movement</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n">
-        <v>-173</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n">
-        <v>-173</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+          <t>Cash flow hedges</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n">
-        <v>-14</v>
-      </c>
+      <c r="D21" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n">
-        <v>-14</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n">
-        <v>-1715</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>-1715</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2019)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Other reserve movements</t>
+          <t>Issue and exchange of other equity instruments</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
+      <c r="C23" s="6" t="n">
+        <v>490</v>
+      </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n">
-        <v>-1</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2022</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>2560</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>-2279</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>15127</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>15413</v>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Equity settled share schemes</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax</t>
+          <t>Other equity instruments coupons paid</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n">
-        <v>177</v>
+        <v>-153</v>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n">
-        <v>1745</v>
-      </c>
+      <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n">
-        <v>1922</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI reserve movement</t>
+          <t>Vesting of employee share schemes</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="E26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n">
+        <v>-12</v>
+      </c>
       <c r="F26" s="6" t="n">
-        <v>63</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Cash flow hedges</t>
+          <t>Dividends paid</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n">
-        <v>1065</v>
-      </c>
-      <c r="E27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>-1050</v>
+      </c>
       <c r="F27" s="6" t="n">
-        <v>1065</v>
+        <v>-1050</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year (FY2023)</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
+          <t>Balance as at 31 December 2019</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="C28" s="5" t="n">
-        <v>177</v>
+        <v>2560</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1128</v>
+        <v>183</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1745</v>
+        <v>13765</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3050</v>
+        <v>16513</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Employee share schemes</t>
+          <t>Profit after tax</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" s="6" t="n">
+        <v>180</v>
+      </c>
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>22</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Issue and redemption of other equity</t>
+          <t>Financial assets at FVOCI reserve movement</t>
         </is>
       </c>
       <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n">
-        <v>-131</v>
-      </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n">
-        <v>-129</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Other equity instruments coupons paid</t>
+          <t>Cash flow hedges</t>
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n">
-        <v>-177</v>
-      </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n">
+        <v>218</v>
+      </c>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n">
-        <v>-177</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n">
-        <v>-1305</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>-1305</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2020)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>670</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Other reserve movements</t>
+          <t>Equity settled share schemes</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2023</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>2429</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>-1151</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>15578</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>16861</v>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n">
+        <v>-180</v>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n">
+        <v>-180</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax</t>
+          <t>Vesting of employee share schemes</t>
         </is>
       </c>
       <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n">
-        <v>198</v>
-      </c>
+      <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n">
-        <v>2422</v>
+        <v>-12</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>2620</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI reserve movement</t>
+          <t>Dividends paid</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n">
-        <v>-33</v>
-      </c>
-      <c r="E37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n">
+        <v>-220</v>
+      </c>
       <c r="F37" s="6" t="n">
-        <v>-33</v>
+        <v>-220</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Cash flow hedges</t>
+          <t>Capital contribution from Barclays PLC</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n">
-        <v>288</v>
-      </c>
-      <c r="E38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n">
+        <v>220</v>
+      </c>
       <c r="F38" s="6" t="n">
-        <v>288</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income for the year (FY2024)</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>255</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>2422</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>2875</v>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Employee share schemes</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>42</v>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2020 / 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>473</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>13989</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>17027</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Issue and exchange of other equity</t>
+          <t>Profit after tax</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n">
-        <v>-4</v>
+        <v>173</v>
       </c>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
+      <c r="E41" s="6" t="n">
+        <v>1696</v>
+      </c>
       <c r="F41" s="6" t="n">
-        <v>-4</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Other equity instruments coupons paid</t>
+          <t>Financial assets at FVOCI reserve movement</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n">
-        <v>-198</v>
-      </c>
-      <c r="D42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n">
+        <v>-67</v>
+      </c>
       <c r="E42" s="6" t="n"/>
       <c r="F42" s="6" t="n">
-        <v>-198</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+          <t>Cash flow hedges</t>
         </is>
       </c>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n">
-        <v>-15</v>
-      </c>
+      <c r="D43" s="6" t="n">
+        <v>-772</v>
+      </c>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="6" t="n">
-        <v>-15</v>
+        <v>-772</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n">
-        <v>-975</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>-975</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2021)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>-839</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>1696</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1030</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Other reserve movements</t>
+          <t>Employee share schemes</t>
         </is>
       </c>
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2024</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>2425</v>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>-896</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>17051</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>18585</v>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n">
+        <v>-173</v>
+      </c>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n">
+        <v>-173</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax</t>
+          <t>Vesting of employee share schemes</t>
         </is>
       </c>
       <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n">
-        <v>214</v>
-      </c>
+      <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n"/>
       <c r="E47" s="6" t="n">
-        <v>2380</v>
+        <v>-11</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2594</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI reserve movement</t>
+          <t>Dividends paid</t>
         </is>
       </c>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="E48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n">
+        <v>-510</v>
+      </c>
       <c r="F48" s="6" t="n">
-        <v>106</v>
+        <v>-510</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Cash flow hedges</t>
+          <t>Capital contribution from Barclays PLC</t>
         </is>
       </c>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n">
-        <v>752</v>
-      </c>
-      <c r="E49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="F49" s="6" t="n">
-        <v>752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Pension remeasurement</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>46</v>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>-366</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>15201</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>17400</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income for the year (FY2025)</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>858</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>2426</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>3498</v>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n">
+        <v>1634</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1807</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Employee share schemes</t>
+          <t>Financial assets at FVOCI reserve movement</t>
         </is>
       </c>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n">
-        <v>72</v>
-      </c>
+      <c r="D52" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="E52" s="6" t="n"/>
       <c r="F52" s="6" t="n">
-        <v>72</v>
+        <v>-198</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Issue and redemption of other equity</t>
+          <t>Cash flow hedges</t>
         </is>
       </c>
       <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n">
-        <v>-198</v>
-      </c>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n">
-        <v>-9</v>
-      </c>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="E53" s="6" t="n"/>
       <c r="F53" s="6" t="n">
-        <v>-207</v>
+        <v>-1715</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Other equity instruments coupons paid</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n">
-        <v>-214</v>
-      </c>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n">
-        <v>-214</v>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2022)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>-1913</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>1634</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-106</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+          <t>Employee share schemes</t>
         </is>
       </c>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="6" t="n"/>
       <c r="D55" s="6" t="n"/>
       <c r="E55" s="6" t="n">
-        <v>-28</v>
+        <v>22</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Dividends paid</t>
+          <t>Other equity instruments coupons paid</t>
         </is>
       </c>
       <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
+      <c r="C56" s="6" t="n">
+        <v>-173</v>
+      </c>
       <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n">
-        <v>-1425</v>
-      </c>
+      <c r="E56" s="6" t="n"/>
       <c r="F56" s="6" t="n">
-        <v>-1425</v>
+        <v>-173</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Other reserve movements</t>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
         </is>
       </c>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6" t="n"/>
       <c r="E57" s="6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>-1715</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>-2279</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>15127</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>15413</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n">
+        <v>1745</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>1128</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n">
+        <v>-131</v>
+      </c>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>-129</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n">
+        <v>-177</v>
+      </c>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n">
+        <v>-177</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n">
+        <v>-1305</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>-1305</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>2429</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>15578</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>16861</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n">
+        <v>2422</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>2422</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Issue and exchange of other equity</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n">
+        <v>-198</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n">
+        <v>-975</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>-975</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>2425</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>-896</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>17051</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>18585</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI reserve movement</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n">
+        <v>752</v>
+      </c>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Pension remeasurement</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>2426</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>-207</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n">
+        <v>-214</v>
+      </c>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="6" t="n">
+        <v>-214</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share based payment schemes</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n">
+        <v>-1425</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>-1425</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n">
         <v>-3</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>Balance as at 31 December 2025</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B94" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C94" s="5" t="n">
         <v>2227</v>
       </c>
-      <c r="D58" s="5" t="n">
+      <c r="D94" s="5" t="n">
         <v>-38</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E94" s="5" t="n">
         <v>18084</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F94" s="5" t="n">
         <v>20278</v>
       </c>
     </row>
-    <row r="60" ht="200" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="96" ht="200" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, pp.197 (income statement), 199 (balance sheet), 200 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, pp.162 (income statement), 164 (balance sheet), 165 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
 FY2021: Barclays Bank UK PLC Annual Report 2021, pp.134 (income statement), 136 (balance sheet), 137 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
-Balance sheet note: FY2021 does not split loans and advances at amortised cost into a bank/customer split, does not disclose a separate debt securities at amortised cost line, and reports deposits at amortised cost as a single combined line - the combined figures appear on their own row for that year only; FY2022-2025 all split these. Income statement note: FY2021 places credit impairment releases/(charges) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; both years' own subtotals are reproduced as reported.</t>
+FY2020: Barclays Bank UK PLC Annual Report 2020, pp.123 (income statement), 125 (balance sheet), 126 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays-Bank-UK-PLC-2020-Annual-Report.pdf
+FY2019: Barclays Bank UK PLC Annual Report 2019, pp.104 (income statement), 106 (balance sheet), 107 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Annual%20Report%202019.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, pp.105 (income statement), 107 (balance sheet), 108 (statement of changes in equity) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
+Balance sheet note: FY2018-FY2021 do not split loans and advances at amortised cost into a bank/customer split, do not disclose a separate debt securities at amortised cost line, and report deposits at amortised cost as a single combined line - the combined figures appear on their own row for those years only; FY2022-2025 all split these. FY2020 is the only year with a separate 'Current tax assets' line (a small net asset position; other years report a nil/immaterial current tax asset position folded into other lines). Income statement note: FY2018-FY2021 place credit impairment charges/(releases) before operating expenses (subtotalled as 'Net operating income'), while FY2022-2025 place it after operating expenses (subtotalled as 'Profit before impairment') - a genuine presentation restructuring, not a transcription error; each year's own subtotals are reproduced as reported. FY2020 and FY2021 both separately disclose a 'Profit on disposal of subsidiaries, associates and joint ventures' line before profit before tax. Figures for FY2018-FY2020 are each reproduced exactly as originally reported in that year's own Annual Report, not as later restated comparatives (e.g. Barclays restated FY2018's tax charge by £28m from FY2019 onward following an IAS 12 update on AT1 coupon tax relief) - consistent with this workbook's sourcing convention throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A96:F96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6859,7 +9005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -6868,6 +9014,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6913,6 +9062,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
         </is>
       </c>
     </row>
@@ -6927,6 +9091,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6949,6 +9116,15 @@
       <c r="F5" s="6" t="n">
         <v>2163</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>367</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>669</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1548</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6971,6 +9147,15 @@
       <c r="F6" s="6" t="n">
         <v>-371</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>1427</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>709</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>624</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6992,6 +9177,15 @@
       </c>
       <c r="F7" s="6" t="n">
         <v>169</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -7009,6 +9203,9 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7031,6 +9228,15 @@
       <c r="F9" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>427</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1665</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7052,6 +9258,15 @@
       </c>
       <c r="F10" s="6" t="n">
         <v>-480</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1217</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-39</v>
       </c>
     </row>
     <row r="11">
@@ -7065,6 +9280,9 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7087,6 +9305,15 @@
       <c r="F12" s="6" t="n">
         <v>322</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>227</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>-531</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7108,6 +9335,15 @@
       </c>
       <c r="F13" s="6" t="n">
         <v>-4591</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-15513</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-10117</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-4022</v>
       </c>
     </row>
     <row r="14">
@@ -7125,6 +9361,11 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n">
+        <v>-421</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7141,6 +9382,11 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n">
+        <v>-171</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7159,6 +9405,13 @@
       <c r="F16" s="6" t="n">
         <v>11050</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>-4614</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1440</v>
+      </c>
+      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7181,6 +9434,11 @@
       <c r="F17" s="6" t="n">
         <v>20197</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>34839</v>
+      </c>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7203,805 +9461,1126 @@
       <c r="F18" s="6" t="n">
         <v>1181</v>
       </c>
+      <c r="G18" s="6" t="n">
+        <v>-768</v>
+      </c>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Net decrease/(increase) in derivative financial instruments</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>906</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>-413</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-1519</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>427</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>-406</v>
+          <t>Net increase in deposits and debt securities in issue (combined, as reported)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>5310</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>6532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Net (increase) in trading portfolio assets</t>
+          <t>Net decrease/(increase) in derivative financial instruments</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>-143</v>
+        <v>906</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-199</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
+        <v>-413</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-1519</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>427</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-406</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-218</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-5854</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Net increase/(decrease) in trading portfolio liabilities</t>
+          <t>Net (increase) in trading portfolio assets</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>182</v>
+        <v>-143</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>-182</v>
+        <v>-199</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n">
+        <v>-151</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Trading assets and liabilities (combined, as reported)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n">
-        <v>455</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>-299</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>-258</v>
+          <t>Net increase/(decrease) in trading portfolio liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-182</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>-496</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Net decrease in financial assets at fair value through the income statement</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>130</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>173</v>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
+          <t>Trading assets and liabilities (combined, as reported)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n">
+        <v>455</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-299</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-258</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-274</v>
+      </c>
+      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Net (decrease)/increase in financial liabilities designated at fair value</t>
+          <t>Net decrease in financial assets at fair value through the income statement</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>-1845</v>
+        <v>130</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>2652</v>
+        <v>173</v>
       </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Financial assets and liabilities at fair value through the income statement (combined, as reported)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n">
-        <v>264</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>787</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>665</v>
-      </c>
+          <t>Net (decrease)/increase in financial liabilities designated at fair value</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-1845</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>2652</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Net (increase) in other assets and liabilities</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>-215</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>-276</v>
-      </c>
+          <t>Financial assets and liabilities at fair value through the income statement (combined, as reported)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n">
-        <v>-52</v>
+        <v>264</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-298</v>
+        <v>787</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-299</v>
+        <v>665</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>309</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1736</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>Net (increase) in other assets and liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>-215</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>-276</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-52</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-298</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-299</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-821</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-1835</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t>Corporate income tax paid</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B28" s="6" t="n">
         <v>-1074</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C28" s="6" t="n">
         <v>-522</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D28" s="6" t="n">
         <v>-583</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E28" s="6" t="n">
         <v>-395</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F28" s="6" t="n">
         <v>-53</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Net cash from operating activities</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>-7860</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>1959</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>-17451</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1466</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>29314</v>
+      <c r="G28" s="6" t="n">
+        <v>-597</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-1086</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>-128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-7860</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1959</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-17451</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1466</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>29314</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>13976</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3111</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-257</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>Investing activities</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Purchase of debt securities at amortised cost</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>-3727</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>-4615</v>
-      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Proceeds from redemption or sale of debt securities at amortised cost</t>
+          <t>Purchase of debt securities at amortised cost</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>8061</v>
+        <v>-3727</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>3932</v>
+        <v>-4615</v>
       </c>
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Debt securities at amortised cost (net, as reported)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n">
-        <v>-178</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>-5796</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>-3695</v>
-      </c>
+          <t>Proceeds from redemption or sale of debt securities at amortised cost</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>8061</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>3932</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Purchase of financial assets at fair value through other comprehensive income</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>-20764</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>-21343</v>
-      </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
+          <t>Debt securities at amortised cost (net, as reported)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n">
+        <v>-178</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-5796</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-3695</v>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Proceeds from sale or redemption of financial assets at fair value through other comprehensive income</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>16812</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>14959</v>
-      </c>
+          <t>Net cash acquired from the acquisition of the UK banking business (FY2018 only)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n">
+        <v>45940</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through other comprehensive income (net, as reported)</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n">
-        <v>-304</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>-6792</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>10125</v>
+          <t>Purchase of financial assets at fair value through other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>-20764</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>-21343</v>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n">
+        <v>-5557</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>-11846</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>-8483</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Financial liabilities designated at fair value (net, as reported)</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n">
-        <v>196</v>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>0</v>
-      </c>
+          <t>Proceeds from sale or redemption of financial assets at fair value through other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>16812</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>14959</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n">
+        <v>7584</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Purchase of property, plant and equipment and investment in intangibles</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>-52</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>-13</v>
-      </c>
+          <t>Financial assets at fair value through other comprehensive income (net, as reported)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n">
-        <v>-25</v>
+        <v>-304</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-13</v>
+        <v>-6792</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>10125</v>
+      </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Acquisition of business, net of cash acquired</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
+          <t>Financial liabilities designated at fair value (net, as reported)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="E38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="6" t="n">
-        <v>-228</v>
-      </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Acquisition of subsidiaries, net of cash acquired</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
+          <t>Purchase of property, plant and equipment and investment in intangibles</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>-52</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>-13</v>
+      </c>
       <c r="D39" s="6" t="n">
-        <v>-2378</v>
+        <v>-25</v>
       </c>
       <c r="E39" s="6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Disposal of subsidiaries, net of cash disposed</t>
+          <t>Proceeds from sale of property, plant and equipment and intangibles (FY2018 only)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n">
-        <v>-141</v>
-      </c>
-      <c r="E40" s="6" t="n">
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Acquisition of business, net of cash acquired</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Net cash from investing activities</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>330</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>-7308</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>-2830</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>-12601</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>6430</v>
-      </c>
+      <c r="C41" s="6" t="n">
+        <v>-228</v>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Acquisition of subsidiaries, net of cash acquired</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
+      <c r="D42" s="6" t="n">
+        <v>-2378</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Dividends paid and other coupon payments on equity instruments</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>-1639</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>-1173</v>
-      </c>
+          <t>Disposal of subsidiaries, net of cash disposed</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
-        <v>-1482</v>
+        <v>-141</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-1888</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>-683</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Capital contribution from Barclays PLC</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n">
-        <v>0</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>-7308</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>-2830</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-12601</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>6430</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-5574</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>-11876</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>45003</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Issuance of subordinated liabilities/debt</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>2277</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>4393</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>829</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>1025</v>
-      </c>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Redemption of subordinated liabilities/debt</t>
+          <t>Dividends paid and other coupon payments on equity instruments</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>-2703</v>
+        <v>-1639</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>-372</v>
+        <v>-1173</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>-1136</v>
+        <v>-1482</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-2017</v>
+        <v>-1888</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-1116</v>
+        <v>-683</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>-400</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>-1203</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>-455</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Issue of shares and other equity instruments</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>990</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>618</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>619</v>
-      </c>
-      <c r="E47" s="6" t="n">
+          <t>Capital contribution from Barclays PLC</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Repurchase/redemption of shares and other equity instruments</t>
+          <t>Issuance of subordinated liabilities/debt</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>-1188</v>
+        <v>3600</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>-622</v>
+        <v>2277</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>-750</v>
+        <v>4393</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="6" t="n"/>
+        <v>829</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>3694</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="I48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Lease liability payments</t>
+          <t>Redemption of subordinated liabilities/debt</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>-41</v>
+        <v>-2703</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>-53</v>
+        <v>-372</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>-63</v>
+        <v>-1136</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-71</v>
-      </c>
-      <c r="F49" s="6" t="n"/>
+        <v>-2017</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>-1116</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>-1425</v>
+      </c>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Vesting of employee share schemes</t>
+          <t>Issue of shares and other equity instruments</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>-28</v>
+        <v>990</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>-15</v>
+        <v>618</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>-16</v>
+        <v>619</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>-11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="I50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>Repurchase/redemption of shares and other equity instruments</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>-1188</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>-622</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>-750</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Lease liability payments</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>-41</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>-53</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>-63</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>-71</v>
+      </c>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of employee share schemes</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>-1009</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>660</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1565</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-3161</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-785</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2077</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>-568</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-465</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t>Effect of exchange rates on cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Net cash from financing activities</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>-1009</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>660</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>1565</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>-3161</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>-785</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Net (decrease)/increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>-8539</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>-4689</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>-18716</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>-14296</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>34959</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at beginning of year</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>35675</v>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>40364</v>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>59080</v>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>73376</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>38417</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at end of year</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>27136</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>35675</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>40364</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>59080</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>73376</v>
-      </c>
+      <c r="G55" s="6" t="n">
+        <v>428</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>-737</v>
+      </c>
+      <c r="I55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year comprise</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
+          <t>Net (decrease)/increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>-8539</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>-4689</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>-18716</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-14296</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>34959</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>10907</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>-16292</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>44281</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
+          <t>Cash and cash equivalents at beginning of year</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>35675</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>40364</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>59080</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>73376</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>38417</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>27510</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>44334</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>27136</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>35675</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>40364</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>59080</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>73376</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>38417</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>28042</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>44334</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year comprise</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
           <t>Cash and balances at central banks</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B60" s="6" t="n">
         <v>21208</v>
       </c>
-      <c r="C57" s="6" t="n">
+      <c r="C60" s="6" t="n">
         <v>29819</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D60" s="6" t="n">
         <v>34948</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E60" s="6" t="n">
         <v>54208</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F60" s="6" t="n">
         <v>69488</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="G60" s="6" t="n">
+        <v>35218</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>24305</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>40669</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Loans and advances to banks with original maturity less than three months</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B61" s="6" t="n">
         <v>178</v>
       </c>
-      <c r="C58" s="6" t="n">
+      <c r="C61" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D61" s="6" t="n">
         <v>291</v>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E61" s="6" t="n">
         <v>347</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F61" s="6" t="n">
         <v>46</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="G61" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Cash collateral balances with central banks with original maturity less than three months</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B62" s="6" t="n">
         <v>5750</v>
       </c>
-      <c r="C59" s="6" t="n">
+      <c r="C62" s="6" t="n">
         <v>5625</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D62" s="6" t="n">
         <v>5125</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E62" s="6" t="n">
         <v>4525</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F62" s="6" t="n">
         <v>3842</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="G62" s="6" t="n">
+        <v>3118</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>3650</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B63" s="5" t="n">
         <v>27136</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C63" s="5" t="n">
         <v>35675</v>
       </c>
-      <c r="D60" s="5" t="n">
+      <c r="D63" s="5" t="n">
         <v>40364</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E63" s="5" t="n">
         <v>59080</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F63" s="5" t="n">
         <v>73376</v>
       </c>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="G63" s="5" t="n">
+        <v>38417</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>28042</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>44334</v>
+      </c>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated cash flow statement, £m:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Annual Report 2025, p.201 (Consolidated cash flow statement) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2025/Barclays-Bank-UK-PLC-Annual-Report-2025.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Annual Report 2023, p.166 (Consolidated cash flow statement) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
 FY2021: Barclays Bank UK PLC Annual Report 2021, p.138 (Consolidated cash flow statement) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
-Note: Barclays changed cash flow statement presentation granularity across these report vintages (e.g. FY2025/FY2024 split some line items — such as repurchase/reverse repurchase agreements and trading portfolio assets/liabilities — that FY2023/FY2022/FY2021 report on a combined basis). Blank cells indicate that year's report did not disclose that specific split; where a coarser combined figure was reported instead, it appears on its own row. Section totals (net cash from operating/investing/financing activities, cash and cash equivalents) are consistent and comparable across all 5 years.</t>
+FY2020: Barclays Bank UK PLC Annual Report 2020, p.127 (Consolidated cash flow statement) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays-Bank-UK-PLC-2020-Annual-Report.pdf
+FY2019: Barclays Bank UK PLC Annual Report 2019, p.108 (Consolidated cash flow statement) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Annual%20Report%202019.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.109 (Consolidated cash flow statement) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
+Note: Barclays changed cash flow statement presentation granularity across these report vintages (e.g. FY2025/FY2024 split some line items — such as repurchase/reverse repurchase agreements and trading portfolio assets/liabilities — that FY2023/FY2022/FY2021 report on a combined basis; FY2019/FY2018 combined deposits and debt securities in issue into one movement, a split FY2020 onward reports separately). Blank cells indicate that year's report did not disclose that specific split; where a coarser combined figure was reported instead, it appears on its own row. Each year's figures are exactly as originally reported in that year's own Annual Report (not a later restated comparative) - Barclays subsequently restated FY2019's cash flow presentation (reclassifying cash collateral within cash and cash equivalents, reducing the FY2019 and FY2018 closing cash balances by £532m and £409m respectively) and separately restated FY2018's other non-cash movements for an exchange-rate effects disclosure introduced from FY2019; as a result FY2018's own reported closing cash balance (£44,334m), FY2019's own reported closing balance (£28,042m), and FY2020's own reported opening balance (£27,510m, i.e. the restated FY2019 closing position) do not exactly chain together - each is reproduced as originally published, consistent with this workbook's sourcing convention throughout. Section totals (net cash from operating/investing/financing activities, cash and cash equivalents) are otherwise consistent and comparable across all 8 years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A65:I65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8013,7 +10592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -8022,6 +10601,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8067,6 +10649,21 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
         </is>
       </c>
     </row>
@@ -8081,6 +10678,9 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8103,6 +10703,15 @@
       <c r="F5" s="6" t="n">
         <v>193961</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>182908</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>171010</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>157753</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -8125,6 +10734,15 @@
       <c r="F6" s="6" t="n">
         <v>24639</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>28078</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>25595</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>29423</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8147,6 +10765,15 @@
       <c r="F7" s="6" t="n">
         <v>3850</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>3812</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3575</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4316</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8168,6 +10795,15 @@
       </c>
       <c r="F8" s="5" t="n">
         <v>222450</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>214798</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>200180</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>191492</v>
       </c>
     </row>
     <row r="9">
@@ -8181,6 +10817,9 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8203,6 +10842,15 @@
       <c r="F10" s="6" t="n">
         <v>395</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>322</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>213</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -8225,6 +10873,15 @@
       <c r="F11" s="6" t="n">
         <v>971</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>1606</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1315</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1459</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8247,6 +10904,15 @@
       <c r="F12" s="6" t="n">
         <v>813</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>1221</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1083</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1269</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -8268,6 +10934,15 @@
       </c>
       <c r="F13" s="5" t="n">
         <v>2179</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3149</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2611</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2927</v>
       </c>
     </row>
     <row r="14">
@@ -8281,6 +10956,9 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8313,6 +10991,21 @@
           <t>1.7%</t>
         </is>
       </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8345,6 +11038,21 @@
           <t>21.1%</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>30.3%</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8375,6 +11083,21 @@
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>1.0%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -8387,13 +11110,16 @@
 FY2023: Annual Report 2023, p.82 — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
 FY2022: Annual Report 2023, p.83 (comparative) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/Barclays-Bank-UK-Annual-Report-2023-Results-committee.pdf
 FY2021: Annual Report 2021, p.66 — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-2021-Annual-Report.pdf
-Note: NPL/coverage ratios are computed here (not the report's own headline ratio, though they tie closely to it - e.g. FY2021 Stage 3 coverage of 21.1% matches the report's own 'Total' Stage 3 coverage figure exactly). Product-level breakdown (e.g. mortgages vs. cards vs. corporate) isn't reproduced since the product taxonomy changed between FY2021 (Home loans / Credit cards &amp; other retail / Wholesale loans) and FY2022-2025 (Retail mortgages / Retail credit cards / Retail other / Corporate loans) - see each year's own source page for the full by-product split.</t>
+FY2020: Annual Report 2020, p.60 (Loans and advances at amortised cost by product) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays-Bank-UK-PLC-2020-Annual-Report.pdf
+FY2019: Annual Report 2019, p.51 (Loans and advances at amortised cost by product) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Annual%20Report%202019.pdf
+FY2018: Annual Report 2018, p.52 (Loans and advances at amortised cost by product, Barclays Bank UK Group table) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
+Note: NPL/coverage ratios are computed here (not the report's own headline ratio, though they tie closely to it - e.g. FY2021 Stage 3 coverage of 21.1% matches the report's own 'Total' Stage 3 coverage figure exactly). Product-level breakdown (e.g. mortgages vs. cards vs. corporate) isn't reproduced since the product taxonomy changed between FY2018-FY2021 (Home loans / Credit cards &amp; other retail / Wholesale loans, called 'Corporate loans' in FY2018) and FY2022-2025 (Retail mortgages / Retail credit cards / Retail other / Corporate loans) - see each year's own source page for the full by-product split.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A19:I19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8405,7 +11131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8414,6 +11140,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8461,6 +11190,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8483,20 +11227,40 @@
       <c r="F4" s="6" t="n">
         <v>10828</v>
       </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="n">
+        <v>11247</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2018 CET1 capital (£10.7bn, unaudited) is disclosed within the FY2018 Annual Report's capital risk section rather than a standalone Pillar 3 report - see p3_sources note on that year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8508,7 +11272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8517,6 +11281,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8564,6 +11331,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8594,6 +11376,21 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -8603,13 +11400,16 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8621,7 +11421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8630,6 +11430,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8677,6 +11480,21 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8698,6 +11516,15 @@
       </c>
       <c r="F4" s="6" t="n">
         <v>13388</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>13807</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>12688</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>12800</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -8706,13 +11533,16 @@
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf</t>
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3602,14 +3603,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Tier 1 Ratio</t>
+          <t>Barclays Bank UK Group — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3663,48 +3664,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>14558</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>14320</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>13067</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13261</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13388</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>13807</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>12688</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>12800</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -3714,8 +3699,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
@@ -3751,14 +3736,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total Capital</t>
+          <t>Barclays Bank UK Group — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3812,32 +3797,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>16996</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>17155</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>15596</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>15828</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>16442</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>17178</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>16012</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>16100</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>17.0%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -3847,8 +3848,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
@@ -3884,14 +3885,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total Capital Ratio</t>
+          <t>Barclays Bank UK Group — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3945,48 +3946,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>21.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>21.3%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>21.3%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>16996</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>17155</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15596</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>15828</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>16442</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>17178</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>16012</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>16100</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -3996,8 +3981,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
@@ -4033,14 +4018,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total RWAs</t>
+          <t>Barclays Bank UK Group — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -4094,32 +4079,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>85065</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>83639</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>72102</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>72719</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>71213</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>72025</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>75010</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>75327</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -4129,8 +4130,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
@@ -4144,6 +4145,139 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>85065</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>83639</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>72102</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>72719</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>71213</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>72025</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>75010</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>75327</v>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4444,235 +4578,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:I12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, £m / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total exposure measure excluding claims on central banks (£m)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>277958</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>268452</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>250163</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>250092</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>241173</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>245176</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>236026</v>
-      </c>
-      <c r="I4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio excluding claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>5.2%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>5.2%</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>5.4%</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio including claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>4.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021-FY2019 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from each year's Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports. FY2018 predates that UK/CRR leverage ratio split at the BBUKPLC entity level (no standalone Pillar 3 report was published for FY2018 - see p3_sources note); the FY2018 Annual Report discloses only a single 'CRR leverage ratio' of 4.9% (with £258bn of CRR leverage exposure), which is presented here on the 'including claims on central banks' row as the closer equivalent - the 'excluding' row and exposure figure are left blank for FY2018 since no comparable UK-basis figure was disclosed that year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures, 'Capital Requirements Regulation (CRR) leverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4701,7 +4606,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — LCR</t>
+          <t>Barclays Bank UK Group — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -4762,112 +4667,126 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value (£m)</t>
+          <t>Total exposure measure excluding claims on central banks (£m)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>64552</v>
+        <v>277958</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>68446</v>
+        <v>268452</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>68533</v>
+        <v>250163</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>81791</v>
+        <v>250092</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>85092</v>
+        <v>241173</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>58035</v>
+        <v>245176</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>41293</v>
+        <v>236026</v>
       </c>
       <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total net cash outflows, adjusted value (£m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>34613</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>33879</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>38057</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>43966</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>41690</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>36246</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>28741</v>
+          <t>Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
       </c>
       <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio (%)</t>
+          <t>Leverage ratio including claims on central banks (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>186.6%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>202.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>186%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>204%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>160%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>144%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>164%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: LCR is computed as a trailing average of the last 12 month-end observations from FY2019 onward. FY2018 predates the BBUKPLC entity's first standalone Pillar 3 report; the FY2018 Annual Report discloses only the headline LCR ratio (164%) within its liquidity risk section, without the underlying weighted HQLA/net cash outflow components in the KM1 format used from FY2019 - those two rows are left blank for FY2018 for that reason.</t>
+          <t>Note: FY2021-FY2019 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from each year's Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports. FY2018 predates that UK/CRR leverage ratio split at the BBUKPLC entity level (no standalone Pillar 3 report was published for FY2018 - see p3_sources note); the FY2018 Annual Report discloses only a single 'CRR leverage ratio' of 4.9% (with £258bn of CRR leverage exposure), which is presented here on the 'including claims on central banks' row as the closer equivalent - the 'excluding' row and exposure figure are left blank for FY2018 since no comparable UK-basis figure was disclosed that year.</t>
         </is>
       </c>
     </row>
@@ -4878,9 +4797,9 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.74 (Annual Report 2018 liquidity risk disclosures, 'Barclays Bank UK Group liquidity coverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures, 'Capital Requirements Regulation (CRR) leverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4835,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — NSFR</t>
+          <t>Barclays Bank UK Group — LCR</t>
         </is>
       </c>
     </row>
@@ -4977,100 +4896,112 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding (£m)</t>
+          <t>Total high-quality liquid assets (HQLA), weighted value (£m)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>257230</v>
+        <v>64552</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>254755</v>
+        <v>68446</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>258620</v>
+        <v>68533</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>266421</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+        <v>81791</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>85092</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>58035</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>41293</v>
+      </c>
       <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding (£m)</t>
+          <t>Total net cash outflows, adjusted value (£m)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>168761</v>
+        <v>34613</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160041</v>
+        <v>33879</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156588</v>
+        <v>38057</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>158156</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+        <v>43966</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>41690</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>36246</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>28741</v>
+      </c>
       <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (%)</t>
+          <t>Liquidity Coverage Ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>152.4%</t>
+          <t>186.6%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>159.3%</t>
+          <t>202.0%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>165%</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>168%</t>
+          <t>186%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>204%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>160%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>144%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>164%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2018-FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2018-FY2021 figures are available.</t>
+          <t>Note: LCR is computed as a trailing average of the last 12 month-end observations from FY2019 onward. FY2018 predates the BBUKPLC entity's first standalone Pillar 3 report; the FY2018 Annual Report discloses only the headline LCR ratio (164%) within its liquidity risk section, without the underlying weighted HQLA/net cash outflow components in the KM1 format used from FY2019 - those two rows are left blank for FY2018 for that reason.</t>
         </is>
       </c>
     </row>
@@ -5081,9 +5012,9 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.74 (Annual Report 2018 liquidity risk disclosures, 'Barclays Bank UK Group liquidity coverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
@@ -5097,6 +5028,209 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>257230</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>254755</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>258620</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>266421</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>168761</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>160041</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>156588</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>158156</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>152.4%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>159.3%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>165%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>168%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2018-FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2018-FY2021 figures are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5238,8 +5372,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
@@ -11131,6 +11265,2035 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group - KM1 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each year from its own Pillar 3 edition's year-end column - two template generations, kept separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>UK KM1 TEMPLATE - AS PUBLISHED FY2022-FY2025 (Table 6: UK KM1 - Key metrics, Parts 1 and 2)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1  Common Equity Tier 1 (CET1) capital (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>12331</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>11895</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10638</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>10701</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>1a  Fully loaded common Equity Tier 1 (CET1) capital (£m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>11862</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10638</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>10628</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2  Tier 1 capital (£m)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>14558</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>14320</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>13067</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>13261</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2a  Fully loaded tier 1 capital (£m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>14287</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>13067</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>13188</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>16996</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>17155</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>15596</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>15828</v>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>3a  Fully loaded total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>17122</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>15596</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>15804</v>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>4  Total risk-weighted exposure amount (£m)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>85065</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>83639</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>72102</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>72719</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4a  Fully loaded total risk-weighted exposure amount (£m)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>83637</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>72102</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>72707</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>5  Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>5a  Fully loaded common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>6  Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>6a  Fully loaded tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>7a  Fully loaded total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b  Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c  Additional T2 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d  Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>12.6%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>8  Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>9  Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>UK 10a  Other Systemically Important Institution buffer (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>11  Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a  Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>18.7%</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>18.7%</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>12  CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio - Barclays Bank UK Group (the first of the two blocks the report prints)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excluding claims on central banks (£m)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>277958</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>268452</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>250163</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>250092</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a  Fully loaded ECL accounting model leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>UK 14b  Leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>UK 14c  Average leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>UK 14d  Average leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>UK 14e  Countercyclical leverage ratio buffer (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio - Barclays Bank UK PLC (the report's SECOND block; different figures, not a repeat)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excluding claims on central banks - Barclays Bank UK PLC (£m)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>278131</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>268870</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>250564</v>
+      </c>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%) - Barclays Bank UK PLC</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a  Fully loaded ECL accounting model leverage ratio excl. central banks (%) - Barclays Bank UK PLC</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>UK 14b  Leverage ratio including claims on central banks (%) - Barclays Bank UK PLC</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio - Barclays Bank UK Group</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>15  Total high-quality liquid assets (HQLA) (Weighted value) (£m)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>64552</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>68446</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>68533</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>81791</v>
+      </c>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a  Cash outflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>36199</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>35356</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>38982</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>45306</v>
+      </c>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b  Cash inflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>1586</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1477</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>925</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>16  Total net cash outflows (adjusted value) (£m)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>34613</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>33879</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>38057</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>43966</v>
+      </c>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>17  Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>186.6%</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>202.0%</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>180%</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>186%</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>17a  Liquidity coverage ratio (%) (period end)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>183%</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio - Barclays Bank UK Group</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>18  Total available stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>257230</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>254755</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>258620</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>266421</v>
+      </c>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>19  Total required stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>168761</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>160041</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>156588</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>158156</v>
+      </c>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>20  NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>152.4%</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>159.3%</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>165%</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>168%</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>BASEL / EU KM1 TEMPLATE - AS PUBLISHED FY2019-FY2021 (Table 4: Key Metrics (KM1/IFRS9-FL)). ROW NUMBERS ARE NOT COMPARABLE WITH THE BLOCK ABOVE.</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>1  Common Equity Tier 1 (CET1) (£m)</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n">
+        <v>10828</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>11247</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>10128</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2  Tier 1 (£m)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n">
+        <v>13388</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>13807</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>12688</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2a  Fully loaded ECL accounting model Tier 1 (£m)</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n">
+        <v>13132</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>13077</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>12498</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n">
+        <v>16442</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>17178</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>16012</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>3a  Fully loaded ECL accounting model total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n">
+        <v>16359</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>16677</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>15990</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>4  Total risk-weighted assets (RWA) (£m)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n">
+        <v>71213</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>72025</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>75010</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>4a  Fully loaded ECL accounting model total risk-weighted assets (RWA) (£m)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n">
+        <v>71116</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>72039</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>75124</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>5  Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>5a  Fully loaded ECL accounting model Common Equity Tier 1 (%)</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>14.9%</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>6  Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>6a  Fully loaded ECL accounting model Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>16.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>7a  Fully loaded ECL accounting model total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>23.0%</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>8  Capital conservation buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>9  Countercyclical buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>11  Total of bank CET1 specific buffer requirements (%) (row 8 + 9 + O-SII)</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>12  CET1 available after meeting the bank's minimum capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>13  Total CRR leverage ratio exposure measure (£m)</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n">
+        <v>324899</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>294242</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>264085</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>14  Transitional CRR leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>IFRS9-FL 17  Leverage ratio as if IFRS 9 or analogous ECLs transitional arrangement had not been applied (%)</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>13a  Total average UK leverage ratio exposure measure (£m)</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n">
+        <v>246849</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>245992</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>240057</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>14a  Transitional average UK leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>13b  Total UK leverage ratio exposure measure (£m)</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="n">
+        <v>241173</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>245176</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>236026</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>14b  Transitional UK leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>15  Total HQLA (£m)</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="6" t="n">
+        <v>85092</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>58035</v>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>41293</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>16  Total net cash outflows (£m)</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n">
+        <v>41690</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>36246</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>28741</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>17  LCR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>204%</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>160%</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>144%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="560" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Source - Barclays Bank UK PLC's own Pillar 3 Reports, each year taken from its OWN edition's year-end column, £m. Page numbers are the reports' own printed folios:
+FY2025: Pillar 3 Report 2025, p.11 (Table 6: UK KM1 - Key metrics - Part 1) and p.12 (Part 2), 'As at 31.12.25' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2024: Pillar 3 Report 2024, p.11 and p.12 (Table 6: UK KM1 - Key metrics (KM1 / IFRS9-FL), Parts 1 and 2), 'As at 31.12.24' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2024Results/FY24-Barclays-Bank-UK-PLC-Pillar-3-Report.pdf
+FY2023: Pillar 3 Report 2023, p.11 and p.12, 'As at 31.12.23' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2022: Pillar 3 Report 2022, p.11 and p.12 (Table 6: UK KM1 - Key metrics (KM1 / IFRS9-FL / Article 468-FL / UK LR) - Part 1), 'As at 31.12.22' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2022/Pillar-3/Barclays-Bank-UK-PLC-Pillar-3-Report-2022.pdf
+FY2021: Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL / Article 468-FL)), '31 Dec 21' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)), '31 December 2020' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)), '31 December 2019' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+THE COLUMNS IN THE SOURCE ARE QUARTER-ENDS, NOT YEARS. Each UK-era edition prints five columns - its own 31 December followed by the three preceding quarter-ends and the prior 31 December (e.g. the 2025 report prints 31.12.25, 30.09.25, 30.06.25, 31.03.25, 31.12.24). Only each edition's own 31 December column is used here. The earlier editions print two to four columns on the same principle (the 2021 report prints 31 Dec 21, 30 June 21, 31 Dec 20, 30 Jun 20). Picking the wrong column would look entirely plausible and be silently wrong, so every figure on this sheet comes from the first column of the edition named above.
+TWO TEMPLATE GENERATIONS, DELIBERATELY NOT MERGED. FY2022-FY2025 use the UK KM1 template; FY2019-FY2021 use the earlier Basel/EU 'KM1 / IFRS9-FL' template, which Barclays captions 'Table 4: Key Metrics'. THE ROW NUMBERS ARE NOT COMPARABLE BETWEEN THE TWO BLOCKS. In the earlier template a bare '7a' is the FULLY LOADED TOTAL CAPITAL RATIO; in the UK template 'UK 7a' is the ADDITIONAL CET1 SREP REQUIREMENT. They are different disclosures sharing a glyph, so the two generations are kept in separate captioned blocks and no row is carried across the break. The earlier template also has no NSFR rows at all (the NSFR became a UK requirement on 1 January 2022), so rows 18-20 are blank for FY2019-FY2021 rather than zero.
+ROWS 13 AND 14 ARE PRINTED TWICE IN EVERY UK-ERA EDITION, FOR TWO DIFFERENT ENTITIES, and the two copies genuinely differ. Part 2 carries a 'Barclays Bank UK Group' leverage block and then a 'Barclays Bank UK PLC' one - at 31.12.25, exposure of £277,958m against £278,131m. Both are reproduced below under their own captions. This workbook is the Barclays Bank UK GROUP consolidation throughout, so the Group block is this entity's own figure and the individual Leverage Ratio sheet carries it; the PLC block is included because the Bank publishes it, not as a substitute for the Group's. The LCR and NSFR blocks are printed once, under a repeated 'Barclays Bank UK Group' sub-heading. Rows UK 14c/14d/14e are printed only in the Group block, so they are blank on the PLC block rather than repeated across it.
+LABEL VARIATION RECORDED, NOT SMOOTHED: the FY2019 edition captions row 11 'Total of bank CET1 specific buffer requirements (%) (row 8 + 9 + SRB)', where the FY2020 and FY2021 editions say '(row 8 + 9 + O-SII)'. The label below is the later wording; the FY2019 figure is its own edition's.
+FY2018 IS NOT SHOWN. Barclays Bank UK PLC published no standalone Pillar 3 report for FY2018 and printed no KM1-shaped table that year, so FY2018 is omitted from this sheet entirely rather than shown as an empty column. Its capital figures remain on the individual metric sheets, cited to the FY2018 Annual Report's capital risk section.
+LATEST-EDITION CHECK, 2026-09-16: the Barclays annual-reports index (https://home.barclays/investor-relations/reports-and-events/annual-reports/) lists 58 Pillar 3 documents. The newest for this entity is FY25-BBUKPLC-Pillar-3.pdf, which this workbook holds; probes for an FY26 edition return an HTML soft-404, consistent with a 31 December year-end. None newer exists.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A87:H87"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11251,8 +13414,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
@@ -11261,155 +13424,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A7:I7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>14.5%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>14.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>14.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>15.6%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11438,14 +13452,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Tier 1 Capital</t>
+          <t>Barclays Bank UK Group — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -11499,32 +13513,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>14558</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>14320</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>13067</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>13261</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13388</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>13807</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>12688</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>12800</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
@@ -11534,8 +13564,8 @@
 FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
 FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.7 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.7 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>

--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -1748,6 +1748,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4283,7 +4284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -4294,7 +4295,6 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4352,11 +4352,6 @@
           <t>FY2019 (£m)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018 (£m)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4385,7 +4380,6 @@
       <c r="H4" s="6" t="n">
         <v>60490</v>
       </c>
-      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4414,7 +4408,6 @@
       <c r="H5" s="6" t="n">
         <v>625</v>
       </c>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4443,7 +4436,6 @@
       <c r="H6" s="6" t="n">
         <v>135</v>
       </c>
-      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4472,7 +4464,6 @@
       <c r="H7" s="6" t="n">
         <v>178</v>
       </c>
-      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4501,7 +4492,6 @@
       <c r="H8" s="6" t="n">
         <v>11617</v>
       </c>
-      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4530,7 +4520,6 @@
       <c r="H9" s="6" t="n">
         <v>1965</v>
       </c>
-      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4559,7 +4548,6 @@
       <c r="H10" s="5" t="n">
         <v>75010</v>
       </c>
-      <c r="I10" s="5" t="n"/>
     </row>
     <row r="12" ht="200" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -4571,13 +4559,17 @@
 FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.11 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
 FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.11 (Table 8: OV1 - Overview of risk weighted assets by risk type and capital requirements) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
 FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf
-FY2018: not available - Barclays Bank UK PLC did not publish a standalone Pillar 3 report for FY2018 (see note above), and the FY2018 Annual Report's capital risk section discloses only the total RWA figure (£75,327m), not a by-risk-type breakdown.</t>
+FY2018: CORRECTED 18 September 2026 (KM1-032). This note previously read 'not available - Barclays Bank UK PLC did not publish a standalone Pillar 3 report for FY2018, and the FY2018 Annual Report's capital risk section discloses only the total RWA figure (£75,327m), not a by-risk-type breakdown'. The first half is true; the second half was FALSE, and it was false because only the SUBSIDIARY's own documents had been searched. A by-risk-type breakdown for Barclays Bank UK PLC is published - in the PARENT's report, which had never been opened: 'Barclays PLC Pillar 3 Report 2018', Table 12a 'Risk weighted assets by significant subsidiaries', printed p.27, which states on p.9 that 'Significant subsidiaries disclosures are included in this report for Barclays Bank PLC and Barclays Bank UK PLC'. Its Barclays Bank UK PLC row, as at 31.12.18, £m: Credit risk Std 3,985; Credit risk A-IRB 59,484; Counterparty credit risk Std 266; CCR A-IRB '-'; Settlement risk '-'; CVA 11; Market risk Std 63; Market risk IMA '-'; Operational risk 11,518; Total RWAs 75,327. Those sum exactly to the 75,327 already carried on the Total RWAs sheet from the Annual Report, which is the control that confirms the row is the right entity's.
+WHY THE COLUMN IS STILL LEFT EMPTY HERE, deliberately and not for want of a source: Table 12a's categories are not this sheet's categories. Because its two credit-risk columns sum with CCR, market and operational risk to the full 75,327, they necessarily SUBSUME the securitisation exposures and the below-threshold 250%-risk-weight amounts that FY2019-FY2025 report on their own rows here. Spreading 3,985 + 59,484 into this sheet's 'Credit risk (excluding CCR)' row would therefore print a figure defined differently from every other year in the same row, which is a worse defect than an empty column - the reproduce-don't-normalise rule. The figures are recorded above so a reader has them.
+BASIS BREAK, also recorded rather than reconciled: Table 12a is Barclays Bank UK PLC on the INDIVIDUAL (PRA solo) basis, whereas this sheet is headed Barclays Bank UK Group consolidated. The parent's own scope-of-consolidation section (printed p.9) gives the reason, and it is also the affirmative explanation for the absence of an FY2018 entity Pillar 3: 'Throughout 2018, Barclays Bank UK PLC (BBUK PLC) was regulated by the Prudential Regulation Authority (PRA) on an individual basis... BBUK PLC Group became regulated by the PRA from 1 January 2019.' The FY2019 first edition is therefore the first year the consolidated basis existed, not merely the first year a document was found.
+TRAP RECORDED FOR ANY LATER PASS: Table 12 on the same printed page is 'RWAs by risk type and BUSINESS' and its 'Barclays UK' row reads 75,181 - the business segment, not the legal entity. The entity figure is 75,327 in Table 12a. The two are adjacent, differ by 146, and the wrong one is entirely plausible.
+Source: https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/Barclays%20PLC%20Pillar%203%20Report%202018.pdf (re-verified 2026-09-18: HTTP 200, application/pdf, %PDF-1.6, 2,174,817 bytes).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -5174,22 +5174,22 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; FY2018 Annual Report (no standalone Pillar 3 that year) names it only as a forthcoming standard (checked 2026-09-19)</t>
         </is>
       </c>
     </row>

--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>4.9%*</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="65" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Leverage ratio shown on the 'excluding claims on central banks' basis for comparability across years (see Leverage Ratio sheet for the 'including' variant and FY2021-FY2018 basis notes); FY2018's figure (marked *) is instead the single 'CRR leverage ratio' disclosed that year (an 'including claims on central banks' basis), since no UK-basis 'excluding' equivalent was published for FY2018 - see the Leverage Ratio sheet's own note. FY2018's 'Other movements, net' in the equity roll-forward is dominated by the £13,044m ordinary share issue and capital reorganisation and £2,169m net equity impact of the UK banking business transfer that established Barclays Bank UK Group in April 2018, not a comparable year-on-year 'other movements' figure.</t>
@@ -3693,7 +3693,7 @@
         <v>12800</v>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -3842,7 +3842,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -3975,7 +3975,7 @@
         <v>16100</v>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -4124,7 +4124,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -4257,7 +4257,7 @@
         <v>75327</v>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -4549,7 +4549,7 @@
         <v>75010</v>
       </c>
     </row>
-    <row r="12" ht="200" customHeight="1">
+    <row r="12" ht="377" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -4775,14 +4775,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021-FY2019 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from each year's Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports. FY2018 predates that UK/CRR leverage ratio split at the BBUKPLC entity level (no standalone Pillar 3 report was published for FY2018 - see p3_sources note); the FY2018 Annual Report discloses only a single 'CRR leverage ratio' of 4.9% (with £258bn of CRR leverage exposure), which is presented here on the 'including claims on central banks' row as the closer equivalent - the 'excluding' row and exposure figure are left blank for FY2018 since no comparable UK-basis figure was disclosed that year.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
+    <row r="9" ht="169" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -4990,14 +4990,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: LCR is computed as a trailing average of the last 12 month-end observations from FY2019 onward. FY2018 predates the BBUKPLC entity's first standalone Pillar 3 report; the FY2018 Annual Report discloses only the headline LCR ratio (164%) within its liquidity risk section, without the underlying weighted HQLA/net cash outflow components in the KM1 format used from FY2019 - those two rows are left blank for FY2018 for that reason.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
+    <row r="9" ht="169" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -5193,14 +5193,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2018-FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2018-FY2021 figures are available.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
+    <row r="9" ht="169" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -5350,14 +5350,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: MREL disclosures are not applicable for Barclays Bank UK Group (the ring-fenced entity) in any of the eight years reviewed; MREL is disclosed at the Barclays PLC group level instead (see Barclays PLC Pillar 3 Report, Table 21: TLAC2).</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" ht="169" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -6589,7 +6589,7 @@
         <v>251305</v>
       </c>
     </row>
-    <row r="46" ht="200" customHeight="1">
+    <row r="46" ht="247" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
@@ -7448,7 +7448,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="33" ht="200" customHeight="1">
+    <row r="33" ht="247" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
@@ -9103,7 +9103,7 @@
         <v>20278</v>
       </c>
     </row>
-    <row r="96" ht="200" customHeight="1">
+    <row r="96" ht="273" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated (audited), £m:
@@ -10690,7 +10690,7 @@
         <v>44334</v>
       </c>
     </row>
-    <row r="65" ht="90" customHeight="1">
+    <row r="65" ht="182" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are Barclays Bank UK Group consolidated cash flow statement, £m:
@@ -13252,7 +13252,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="560" customHeight="1">
+    <row r="87" ht="409" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
           <t>Source - Barclays Bank UK PLC's own Pillar 3 Reports, each year taken from its OWN edition's year-end column, £m. Page numbers are the reports' own printed folios:
@@ -13392,14 +13392,14 @@
         <v>10700</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2018 CET1 capital (£10.7bn, unaudited) is disclosed within the FY2018 Annual Report's capital risk section rather than a standalone Pillar 3 report - see p3_sources note on that year.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" ht="169" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
@@ -13549,7 +13549,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:

--- a/banks/BARCLAYS FINANCIALS.xlsx
+++ b/banks/BARCLAYS FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3604,14 +3605,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Tier 1 Capital</t>
+          <t>Barclays Bank UK Group — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3665,32 +3666,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>14558</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>14320</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>13067</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>13261</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13388</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>13807</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>12688</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>12800</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="169" customHeight="1">
@@ -3737,14 +3754,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Tier 1 Ratio</t>
+          <t>Barclays Bank UK Group — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3798,48 +3815,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>14558</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>14320</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>13067</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13261</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13388</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>13807</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>12688</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>12800</v>
       </c>
     </row>
     <row r="6" ht="169" customHeight="1">
@@ -3886,14 +3887,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total Capital</t>
+          <t>Barclays Bank UK Group — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3947,32 +3948,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>16996</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>17155</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>15596</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>15828</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>16442</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>17178</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>16012</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>16100</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>17.0%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="169" customHeight="1">
@@ -4019,14 +4036,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total Capital Ratio</t>
+          <t>Barclays Bank UK Group — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -4080,48 +4097,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>21.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>21.3%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>21.3%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>16996</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>17155</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15596</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>15828</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>16442</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>17178</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>16012</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>16100</v>
       </c>
     </row>
     <row r="6" ht="169" customHeight="1">
@@ -4168,14 +4169,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — Total RWAs</t>
+          <t>Barclays Bank UK Group — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, £m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -4229,32 +4230,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>85065</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>83639</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>72102</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>72719</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>71213</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>72025</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>75010</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>75327</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="169" customHeight="1">
@@ -4279,6 +4296,139 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>85065</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>83639</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>72102</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>72719</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>71213</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>72025</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>75010</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>75327</v>
+      </c>
+    </row>
+    <row r="6" ht="169" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4570,235 +4720,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:H12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, £m / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total exposure measure excluding claims on central banks (£m)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>277958</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>268452</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>250163</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>250092</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>241173</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>245176</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>236026</v>
-      </c>
-      <c r="I4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio excluding claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>5.2%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>5.2%</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>5.4%</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio including claims on central banks (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>4.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021-FY2019 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from each year's Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports. FY2018 predates that UK/CRR leverage ratio split at the BBUKPLC entity level (no standalone Pillar 3 report was published for FY2018 - see p3_sources note); the FY2018 Annual Report discloses only a single 'CRR leverage ratio' of 4.9% (with £258bn of CRR leverage exposure), which is presented here on the 'including claims on central banks' row as the closer equivalent - the 'excluding' row and exposure figure are left blank for FY2018 since no comparable UK-basis figure was disclosed that year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="169" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures, 'Capital Requirements Regulation (CRR) leverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4827,7 +4748,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — LCR</t>
+          <t>Barclays Bank UK Group — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -4888,112 +4809,126 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value (£m)</t>
+          <t>Total exposure measure excluding claims on central banks (£m)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>64552</v>
+        <v>277958</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>68446</v>
+        <v>268452</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>68533</v>
+        <v>250163</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>81791</v>
+        <v>250092</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>85092</v>
+        <v>241173</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>58035</v>
+        <v>245176</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>41293</v>
+        <v>236026</v>
       </c>
       <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total net cash outflows, adjusted value (£m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>34613</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>33879</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>38057</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>43966</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>41690</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>36246</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>28741</v>
+          <t>Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
       </c>
       <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio (%)</t>
+          <t>Leverage ratio including claims on central banks (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>186.6%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>202.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>186%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>204%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>160%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>144%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>164%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>4.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: LCR is computed as a trailing average of the last 12 month-end observations from FY2019 onward. FY2018 predates the BBUKPLC entity's first standalone Pillar 3 report; the FY2018 Annual Report discloses only the headline LCR ratio (164%) within its liquidity risk section, without the underlying weighted HQLA/net cash outflow components in the KM1 format used from FY2019 - those two rows are left blank for FY2018 for that reason.</t>
+          <t>Note: FY2021-FY2019 exposure/ratios use the 'UK leverage ratio (Transitional)' and 'CRR leverage ratio (Transitional)' rows from each year's Pillar 3 report as the closest equivalents to the 'excluding'/'including claims on central banks' framing introduced in later reports. FY2018 predates that UK/CRR leverage ratio split at the BBUKPLC entity level (no standalone Pillar 3 report was published for FY2018 - see p3_sources note); the FY2018 Annual Report discloses only a single 'CRR leverage ratio' of 4.9% (with £258bn of CRR leverage exposure), which is presented here on the 'including claims on central banks' row as the closer equivalent - the 'excluding' row and exposure figure are left blank for FY2018 since no comparable UK-basis figure was disclosed that year.</t>
         </is>
       </c>
     </row>
@@ -5006,7 +4941,7 @@
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
 FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
 FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.74 (Annual Report 2018 liquidity risk disclosures, 'Barclays Bank UK Group liquidity coverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures, 'Capital Requirements Regulation (CRR) leverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
@@ -5042,7 +4977,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — NSFR</t>
+          <t>Barclays Bank UK Group — LCR</t>
         </is>
       </c>
     </row>
@@ -5103,100 +5038,112 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding (£m)</t>
+          <t>Total high-quality liquid assets (HQLA), weighted value (£m)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>257230</v>
+        <v>64552</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>254755</v>
+        <v>68446</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>258620</v>
+        <v>68533</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>266421</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+        <v>81791</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>85092</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>58035</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>41293</v>
+      </c>
       <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding (£m)</t>
+          <t>Total net cash outflows, adjusted value (£m)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>168761</v>
+        <v>34613</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>160041</v>
+        <v>33879</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>156588</v>
+        <v>38057</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>158156</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+        <v>43966</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>41690</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>36246</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>28741</v>
+      </c>
       <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (%)</t>
+          <t>Liquidity Coverage Ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>152.4%</t>
+          <t>186.6%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>159.3%</t>
+          <t>202.0%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>165%</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>168%</t>
+          <t>186%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
+          <t>204%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
+          <t>160%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
+          <t>144%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; FY2018 Annual Report (no standalone Pillar 3 that year) names it only as a forthcoming standard (checked 2026-09-19)</t>
+          <t>164%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2018-FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2018-FY2021 figures are available.</t>
+          <t>Note: LCR is computed as a trailing average of the last 12 month-end observations from FY2019 onward. FY2018 predates the BBUKPLC entity's first standalone Pillar 3 report; the FY2018 Annual Report discloses only the headline LCR ratio (164%) within its liquidity risk section, without the underlying weighted HQLA/net cash outflow components in the KM1 format used from FY2019 - those two rows are left blank for FY2018 for that reason.</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5156,7 @@
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
 FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
 FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.74 (Annual Report 2018 liquidity risk disclosures, 'Barclays Bank UK Group liquidity coverage ratio') — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5245,14 +5192,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank UK Group — MREL Ratio</t>
+          <t>Barclays Bank UK Group — NSFR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis</t>
+          <t>Consolidated basis, £m / %</t>
         </is>
       </c>
     </row>
@@ -5306,63 +5253,109 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed at this level</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: MREL disclosures are not applicable for Barclays Bank UK Group (the ring-fenced entity) in any of the eight years reviewed; MREL is disclosed at the Barclays PLC group level instead (see Barclays PLC Pillar 3 Report, Table 21: TLAC2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="169" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Total available stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>257230</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>254755</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>258620</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>266421</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>168761</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>160041</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>156588</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>158156</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>152.4%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>159.3%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>165%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>168%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; this year's Pillar 3 has no NSFR and the annual report names it only as a forthcoming standard (checked 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; FY2018 Annual Report (no standalone Pillar 3 that year) names it only as a forthcoming standard (checked 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: NSFR is computed as a trailing average of the last four spot quarter-end positions. It was not a Pillar 3 disclosure requirement as at FY2018-FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2018-FY2021 figures are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="169" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.12 (Table 6: KM1 - Key metrics - Part 2) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
 FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
 FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
 FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
@@ -5372,8 +5365,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:I5"/>
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6606,6 +6599,163 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A46:I46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed at this level</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: MREL disclosures are not applicable for Barclays Bank UK Group (the ring-fenced entity) in any of the eight years reviewed; MREL is disclosed at the Barclays PLC group level instead (see Barclays PLC Pillar 3 Report, Table 21: TLAC2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="169" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
+FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
+FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
+FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
+FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
+FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11257,6 +11407,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank UK Group — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.35%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>14.78%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>11.91%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>11.01%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>10.86%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>12.79%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>14.10%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>11.40%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>11.72%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>10.74%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>6.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Return on Assets (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="208" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Return on Assets: “Return on Assets is calculated as profit after tax divided by total balance sheet assets at the balance sheet date.”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2022, where return on equity is 11.01% on an average basis and 11.72% on a year-end basis.
+FY2018 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2018 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2018 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2024 Return on Assets 0.9%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit after tax” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Barclays Bank UK Group's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Barclays Bank UK Group's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘BARCLAYS’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13280,7 +13742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13419,153 +13881,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank UK Group — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>14.5%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>14.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>14.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>15.6%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="169" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank UK Group consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: Barclays Bank UK PLC Pillar 3 Report 2025, p.11 (Table 6: KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBUKPLC-Pillar-3.pdf
-FY2023 &amp; FY2022: Barclays Bank UK PLC Pillar 3 Report 2023, p.11 (Table 6: UK KM1 - Key metrics - Part 1) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-UK-Pillar-3-Report-2023.pdf
-FY2021: Barclays Bank UK PLC Pillar 3 Report 2021, p.9 (Table 4: Key Metrics (KM1 / IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-UK-PLC-Pillar-3-Report-2021.pdf
-FY2020: Barclays Bank UK PLC Pillar 3 Report 2020, p.8 (Table 4: Key Metrics (KM1/IFRS 9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2020/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report%202020.pdf
-FY2019: Barclays Bank UK PLC Pillar 3 Report 2019, p.8 (Table 4: Key Metrics (KM1/IFRS9-FL)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2019/Barclays%20Bank%20UK%20PLC%20Pillar%203%20Report.pdf
-FY2018: Barclays Bank UK PLC Annual Report 2018, p.80 (Annual Report 2018 capital risk disclosures (no standalone Pillar 3 report)) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2018/2018-barclays-bank-uk-plc-annual-report.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:I6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>